--- a/exports/pm06_status_codes.xlsx
+++ b/exports/pm06_status_codes.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Фазы заказа" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Пользовательские статусы'!$A$1:$W$68</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Системные статусы'!$A$1:$W$39</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Пользовательские статусы'!$A$1:$X$68</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Системные статусы'!$A$1:$X$39</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="428">
   <si>
     <t xml:space="preserve">Коды статусов заказов ТОРО в выгрузке PM-06</t>
   </si>
@@ -38,7 +38,10 @@
     <t xml:space="preserve">Что нужно сделать</t>
   </si>
   <si>
-    <t xml:space="preserve">На листах «Системные статусы» и «Пользовательские статусы» заполните жёлтые колонки:</t>
+    <t xml:space="preserve">Расшифровки уже подставлены из документации SAP (КД, памятки, скриншот окна статусов). Заполнять нужно только строки, где «Уверенность» выделена красным</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(вероятно / гипотеза / неизвестно) — в них жёлтые колонки:</t>
   </si>
   <si>
     <t xml:space="preserve">  • «Описание» — полный текст статуса из SAP (таблица TJ02T для системных, TJ30T для пользовательских) и что он значит на практике;</t>
@@ -59,7 +62,7 @@
     <t xml:space="preserve">Код</t>
   </si>
   <si>
-    <t xml:space="preserve">Наша расшифровка</t>
+    <t xml:space="preserve">Текст SAP</t>
   </si>
   <si>
     <t xml:space="preserve">Описание (заполнить)</t>
@@ -71,160 +74,193 @@
     <t xml:space="preserve">Комментарий</t>
   </si>
   <si>
+    <t xml:space="preserve">ОШОЗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;полный текст статуса из SAP и что он означает&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">нет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;например: ставится автоматически при ошибке калькуляции&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Как читать расчётные колонки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказов по годам — сколько заказов с этим кодом в выгрузке каждого года; «Всего» — сумма по годам (формула).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля с фактом — доля заказов, по которым есть фактические затраты МТР, УСО или услуг.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля в фазе — как заказы с этим кодом распределены по фазам. Фаза задаётся одним из кодов ОТКР, ДЕБЛ (ЧДЕБ), ТЗКР, ЗАКР; у каждого заказа он ровно один. «Нет статуса» — позиции 2027 года без заказа SAP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уверенность нашей расшифровки: «подтверждено» — из спецификации отчёта (лист «Алгоритмы выборки» в самой выгрузке); «вероятно» — стандартная расшифровка SAP, по вашей системе не проверена; «гипотеза» — вывод по данным; «неизвестно» — расшифровки нет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Примеры — номера заказов (год, площадка, номер) для проверки в SAP (IW33).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Суммы — план и факт МТР + УСО в миллионах рублей по всем заказам с кодом (коды у заказа пересекаются, поэтому суммы по кодам не складываются).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказов 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказов 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказов 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказов 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказов 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказов 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказов всего</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля с фактом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">План, млн ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Факт, млн ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля в фазе ОТКР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля в фазе ДЕБЛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля в фазе ТЗКР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля в фазе ЗАКР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля в фазе нет статуса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Смысл, кто ставит</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Источник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уверенность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Примеры заказов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОБСЗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стоит на всех заказах SAP с момента создания. Расшифровки в документации нет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">вывод по данным PM-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">неизвестно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1500014723; 2024 1100 1100884889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПКАЛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПредвКалькуляция проведена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически при сохранении: рассчитаны плановые затраты.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19; скриншот окна статусов SAP (Статусы.docx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">подтверждено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ДМНП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ДоступностьМтрл не проверена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически, если проверка доступности материалов не запускалась.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРВВ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Правило расчета введено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказу присвоено правило расчёта затрат.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JBFI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Задача завершена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Текст из SAP. Стоит на 99 % технически и коммерчески закрытых заказов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">скриншот окна статусов SAP (Статусы.docx); вывод по данным PM-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">текст подтверждён</t>
+  </si>
+  <si>
     <t xml:space="preserve">ЗАКР</t>
   </si>
   <si>
-    <t xml:space="preserve">Закрыт (коммерческое закрытие)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLSD — Закрыт: заказ закрыт коммерчески, затраты рассчитаны, изменения невозможны</t>
-  </si>
-  <si>
-    <t xml:space="preserve">да</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Остаток «план − факт» по заказу потребностью не считать</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Как читать расчётные колонки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказов по годам — сколько заказов с этим кодом в выгрузке каждого года; «Всего» — сумма по годам (формула).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доля с фактом — доля заказов, по которым есть фактические затраты МТР, УСО или услуг.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доля в фазе — как заказы с этим кодом распределены по фазам. Фаза задаётся одним из кодов ОТКР, ДЕБЛ (ЧДЕБ), ТЗКР, ЗАКР; у каждого заказа он ровно один. «Нет статуса» — позиции 2027 года без заказа SAP.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Уверенность нашей расшифровки: «подтверждено» — из спецификации отчёта (лист «Алгоритмы выборки» в самой выгрузке); «вероятно» — стандартная расшифровка SAP, по вашей системе не проверена; «гипотеза» — вывод по данным; «неизвестно» — расшифровки нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Примеры — номера заказов (год, площадка, номер) для проверки в SAP (IW33).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Суммы — план и факт МТР + УСО в миллионах рублей по всем заказам с кодом (коды у заказа пересекаются, поэтому суммы по кодам не складываются).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказов 2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказов 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказов 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказов 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказов 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказов 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказов всего</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доля с фактом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">План, млн ₽</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Факт, млн ₽</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доля в фазе ОТКР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доля в фазе ДЕБЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доля в фазе ТЗКР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доля в фазе ЗАКР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доля в фазе нет статуса</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Источник</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Уверенность</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Примеры заказов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОБСЗ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">неизвестно</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1500014723; 2024 1100 1100884889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПКАЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Предварительно калькулирован</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стандарт SAP (PRC)</t>
+    <t xml:space="preserve">Закрыто</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коммерческое закрытие; только после ТЗКР, сальдо заказа = 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19; спецификация отчёта, лист «Алгоритмы выборки»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ДВМА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вероятно «Движение материала проведено» (GMPS): у 99–100 % таких заказов есть факт.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">стандартная расшифровка SAP; вывод по данным PM-06</t>
   </si>
   <si>
     <t xml:space="preserve">вероятно</t>
   </si>
   <si>
-    <t xml:space="preserve">ДМНП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доступность материала не проверена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стандарт SAP (MANC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПРВВ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Правило расчёта введено</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стандарт SAP (SETC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JBFI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">спецификация отчёта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">подтверждено</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ДВМА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Движение материала проведено</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стандарт SAP (GMPS)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ПДТВ</t>
   </si>
   <si>
-    <t xml:space="preserve">Подтверждён</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стандарт SAP (CNF)</t>
+    <t xml:space="preserve">Подтверждено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Введены подтверждения по всем операциям; только при ДЕБЛ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1100884694; 2024 1100 1101259617</t>
@@ -233,25 +269,46 @@
     <t xml:space="preserve">РБЗК</t>
   </si>
   <si>
+    <t xml:space="preserve">Работа закрыта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Текст из SAP. Появляется с 2024 года вместе с АНРЕ и АРВО на закрываемых заказах.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">текст подтверждён, назначение — вывод по данным</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024 1100 1101813707; 2025 1100 1101878222; 2026 1100 1200365166</t>
   </si>
   <si>
     <t xml:space="preserve">АНРЕ</t>
   </si>
   <si>
+    <t xml:space="preserve">Анализ результатов проведен</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Текст из SAP. С 2024 года, всегда вместе с АРВО.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">скриншот окна статусов SAP (Статусы.docx)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024 1100 1101813707; 2025 1100 1101878222; 2026 1100 1102226644</t>
   </si>
   <si>
     <t xml:space="preserve">АРВО</t>
   </si>
   <si>
+    <t xml:space="preserve">С 2024 года, всегда вместе с АНРЕ и РБЗК. Расшифровки в документации нет.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ПЕЧТ</t>
   </si>
   <si>
-    <t xml:space="preserve">Напечатан</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стандарт SAP (PRT)</t>
+    <t xml:space="preserve">Напечатано</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказ распечатан; только при ДЕБЛ.</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1100759462; 2023 1100 1100877483; 2024 1100 1101392569</t>
@@ -260,16 +317,22 @@
     <t xml:space="preserve">KKMP</t>
   </si>
   <si>
+    <t xml:space="preserve">Без компонентов материала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически, если в заказе нет материалов.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100771390; 2023 1100 1100910354; 2024 1100 1200252523</t>
   </si>
   <si>
     <t xml:space="preserve">ОТКР</t>
   </si>
   <si>
-    <t xml:space="preserve">Открыт (создан, не деблокирован)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">спецификация отчёта, лист «Алгоритмы выборки»</t>
+    <t xml:space="preserve">Открыто</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставится автоматически при создании заказа. Заказ ещё не деблокирован.</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1800010075; 2023 1100 1101471084; 2024 1100 1101879322</t>
@@ -278,10 +341,13 @@
     <t xml:space="preserve">ЧПЕЧ</t>
   </si>
   <si>
-    <t xml:space="preserve">Частично напечатан</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стандарт SAP (PPRT)</t>
+    <t xml:space="preserve">Частично напечатано</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Напечатана часть документов заказа.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">стандартная расшифровка SAP</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1100386576; 2023 1100 1101045267; 2024 1100 1100884889</t>
@@ -290,10 +356,10 @@
     <t xml:space="preserve">ЧПДТ</t>
   </si>
   <si>
-    <t xml:space="preserve">Частично подтверждён</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стандарт SAP (PCNF)</t>
+    <t xml:space="preserve">Частично подтверждено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подтверждена часть операций; только при ДЕБЛ.</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1100317458; 2023 1100 1100877483; 2024 1100 1100884889</t>
@@ -302,13 +368,28 @@
     <t xml:space="preserve">СРНА</t>
   </si>
   <si>
+    <t xml:space="preserve">Сроки не актуальны</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Даты заказа не пересчитаны (NTUP).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">скриншот окна статусов SAP (Статусы.docx); стандартная расшифровка SAP</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100386045; 2023 1100 1101340657; 2024 1100 1101392569</t>
   </si>
   <si>
     <t xml:space="preserve">ТЗКР</t>
   </si>
   <si>
-    <t xml:space="preserve">Технически закрыт</t>
+    <t xml:space="preserve">Технически закрыто</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Техническое закрытие: работы выполнены, факт проведён. Ставит планировщик ТОиР; только при ДЕБЛ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19; ТОиР-84; памятка ТОиР-77 «Ключевые отличия SAP ТОРО в АО Развитие»; спецификация отчёта, лист «Алгоритмы выборки»</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1200090088; 2023 1100 1003960; 2024 1100 1101926982</t>
@@ -317,64 +398,85 @@
     <t xml:space="preserve">#</t>
   </si>
   <si>
-    <t xml:space="preserve">Нет статуса: позиция графика ППР без заказа SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">вывод по данным (только 2027, номера 110000…)</t>
+    <t xml:space="preserve">нет статуса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Позиция графика ППР, по которой заказ SAP ещё не создан. Только 2027 год, номера из диапазона планов ТОРО 100000000000–199999999999.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">вывод по данным PM-06; КД ERP.13.9.2.52 табл. 25 (диапазон номеров планов ТОРО); ТОиР-82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гипотеза, подкреплена документацией</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027 1100 110000033568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72 % на открытых заказах плана 2027 года. Расшифровки в документации нет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100317017; 2023 1100 1200159659; 2024 1100 1900003788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ДЕБЛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Деблокировано</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказ передан в работу: разрешены печать и фактические проводки.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 4000018911; 2023 1100 4000036509; 2024 1100 4000040107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95 % на технически закрытых заказах. Расшифровки в документации нет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1100 1101948705; 2026 1100 1102683820; 2025 1200 1101767962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98 % на заказах ЕТО (AETG): вероятно, передача на мобильное устройство.</t>
   </si>
   <si>
     <t xml:space="preserve">гипотеза</t>
   </si>
   <si>
-    <t xml:space="preserve">2027 1100 110000033568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОШОЗ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100317017; 2023 1100 1200159659; 2024 1100 1900003788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ДЕБЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Деблокирован (в работе)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 4000018911; 2023 1100 4000036509; 2024 1100 4000040107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1100 1101948705; 2026 1100 1102683820; 2025 1200 1101767962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOBI</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025 1100 1600682946; 2026 1100 1600871206; 2022 1200 1100356263</t>
   </si>
   <si>
     <t xml:space="preserve">НКС</t>
   </si>
   <si>
+    <t xml:space="preserve">97 % на коммерчески закрытых заказах. Расшифровки в документации нет.</t>
+  </si>
+  <si>
     <t xml:space="preserve">КООП</t>
   </si>
   <si>
+    <t xml:space="preserve">Только сетевые графики P030/P310. Расшифровки в документации нет.</t>
+  </si>
+  <si>
     <t xml:space="preserve">НОСР</t>
   </si>
   <si>
+    <t xml:space="preserve">Только сетевые графики P310. Расшифровки в документации нет.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 4000009964; 2023 1300 4000030482; 2022 1400 4000018391</t>
   </si>
   <si>
     <t xml:space="preserve">ДВЖМ</t>
   </si>
   <si>
-    <t xml:space="preserve">Движение материала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стандарт SAP</t>
+    <t xml:space="preserve">Рядом с ДВМА (движение материала). Расшифровки в документации нет.</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1100439271; 2023 1100 1100883152; 2024 1100 1100884889</t>
@@ -383,12 +485,18 @@
     <t xml:space="preserve">ПОСТ</t>
   </si>
   <si>
+    <t xml:space="preserve">Вероятно «Поставлено» (DLV); только на заказах вспомогательного производства ZP01.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1001765; 2023 1100 1003960; 2024 1100 1004640</t>
   </si>
   <si>
     <t xml:space="preserve">РОСГ</t>
   </si>
   <si>
+    <t xml:space="preserve">Только заказы вспомогательного производства ZP01. Расшифровки в документации нет.</t>
+  </si>
+  <si>
     <t xml:space="preserve">НРАК</t>
   </si>
   <si>
@@ -398,10 +506,10 @@
     <t xml:space="preserve">ЧДЕБ</t>
   </si>
   <si>
-    <t xml:space="preserve">Частично деблокирован</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стандарт SAP (PREL)</t>
+    <t xml:space="preserve">Частично деблокировано</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В выгрузке встречается только на сетевых графиках P310/P030.</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 4000009964; 2025 1100 4000053526; 2026 1100 4000065249</t>
@@ -410,30 +518,48 @@
     <t xml:space="preserve">ДЕБО</t>
   </si>
   <si>
+    <t xml:space="preserve">48 открытых заказов. Расшифровки в документации нет.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2027 1100 1500038731; 2026 1400 1102333756; 2027 1400 1500030652</t>
   </si>
   <si>
     <t xml:space="preserve">МАПД</t>
   </si>
   <si>
+    <t xml:space="preserve">Материал подтвержден</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверка доступности запущена, все материалы подтверждены.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1002218; 2023 1100 1004152</t>
   </si>
   <si>
     <t xml:space="preserve">ЗАОЦ</t>
   </si>
   <si>
+    <t xml:space="preserve">11 заказов, в основном ASR1. Расшифровки в документации нет.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1200100075; 2026 1100 910100045331; 2023 1300 910100027096</t>
   </si>
   <si>
     <t xml:space="preserve">ЗТНА</t>
   </si>
   <si>
+    <t xml:space="preserve">Только сетевые графики P030. Расшифровки в документации нет.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 4000015921; 2024 1100 4000041533; 2022 1400 4000018125</t>
   </si>
   <si>
     <t xml:space="preserve">НПДМ</t>
   </si>
   <si>
+    <t xml:space="preserve">3 закрытых заказа. Расшифровки в документации нет.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 2000021301; 2023 1400 2000045981</t>
   </si>
   <si>
@@ -443,7 +569,7 @@
     <t xml:space="preserve">Нет материала</t>
   </si>
   <si>
-    <t xml:space="preserve">стандарт SAP (NMAT)</t>
+    <t xml:space="preserve">2 заказа 2022 года; стандартный системный статус NMAT. В актуальной схеме «Нет материалов» — пользовательский статус.</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1002186</t>
@@ -452,13 +578,31 @@
     <t xml:space="preserve">СГГС</t>
   </si>
   <si>
+    <t xml:space="preserve">Согл Гл спец ТОиР БЕ ГОК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Порядковый №4: согласовано главным специалистом ТОиР.</t>
+  </si>
+  <si>
     <t xml:space="preserve">МТРЦ</t>
   </si>
   <si>
+    <t xml:space="preserve">МТР оценены</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически: цены всех МТР утверждены.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19 (табл. 18)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ГОД</t>
   </si>
   <si>
-    <t xml:space="preserve">Включён в годовой план</t>
+    <t xml:space="preserve">Заказ включен в годовой план</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставит планировщик ТОиР после включения в годовой план.</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1100884694; 2024 1100 1100884889</t>
@@ -467,25 +611,70 @@
     <t xml:space="preserve">ПРНТ</t>
   </si>
   <si>
+    <t xml:space="preserve">Работы приняты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Инженер ТОиР принял работы; условие ТЗКР для заказов с УСО.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19 (табл. 18); ТОиР-77</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100480386; 2023 1100 1100821797; 2024 1100 1900003446</t>
   </si>
   <si>
     <t xml:space="preserve">ГИП</t>
   </si>
   <si>
+    <t xml:space="preserve">Согласован Главным инженером</t>
+  </si>
+  <si>
+    <t xml:space="preserve">После утверждения плана-графика главным инженером и согласования ПТО.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ПРСЗ</t>
   </si>
   <si>
+    <t xml:space="preserve">Принято службой заказчика</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Приёмка работ АО «Развитие» службой заказчика БЕ; только после ТЗКР. Блокирует дальнейшие проводки.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">памятка ТОиР-77 «Ключевые отличия SAP ТОРО в АО Развитие»; ТОиР-84</t>
+  </si>
+  <si>
     <t xml:space="preserve">ВСБЕ</t>
   </si>
   <si>
+    <t xml:space="preserve">Заказ выставлен в БЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически при регистрации выручки (ZMM_370); после него снять ПРСЗ нельзя.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">памятка ТОиР-77 «Ключевые отличия SAP ТОРО в АО Развитие»; скриншот окна статусов SAP (Статусы.docx)</t>
+  </si>
+  <si>
     <t xml:space="preserve">СРОЧ</t>
   </si>
   <si>
+    <t xml:space="preserve">Срочная закупка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически: дата потребности раньше даты поставки МТР (с учётом остатков и LT).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19 (табл. 18); ТОиР-86, ТОиР-96</t>
+  </si>
+  <si>
     <t xml:space="preserve">УТВГ</t>
   </si>
   <si>
-    <t xml:space="preserve">Утверждён в годовом плане</t>
+    <t xml:space="preserve">Утвержден в программе ремонтов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставит старший планировщик после утверждения годового плана-графика.</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1100316544; 2023 1100 1100884694; 2024 1100 1100884889</t>
@@ -494,7 +683,10 @@
     <t xml:space="preserve">МЕС</t>
   </si>
   <si>
-    <t xml:space="preserve">Включён в месячный план</t>
+    <t xml:space="preserve">Заказ включен в месячный план</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставит планировщик.</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1100884048; 2024 1100 1100884889</t>
@@ -503,19 +695,22 @@
     <t xml:space="preserve">УТВМ</t>
   </si>
   <si>
-    <t xml:space="preserve">Утверждён в месячном плане</t>
+    <t xml:space="preserve">Утв в месячном плане-графике</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставит старший планировщик.</t>
   </si>
   <si>
     <t xml:space="preserve">УТВН</t>
   </si>
   <si>
-    <t xml:space="preserve">Утверждён в недельном плане</t>
+    <t xml:space="preserve">Утв в недельном плане-графике</t>
   </si>
   <si>
     <t xml:space="preserve">НЕД</t>
   </si>
   <si>
-    <t xml:space="preserve">Включён в недельный план</t>
+    <t xml:space="preserve">Заказ включен в недельный план</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1100910354; 2024 1100 1101259617</t>
@@ -524,297 +719,567 @@
     <t xml:space="preserve">ПЗТГ</t>
   </si>
   <si>
+    <t xml:space="preserve">Согласован ПЗТГ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согласован прогноз завершения текущего года; ставится автоматически при отправке в ПТО.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19; КД ERP.13.9.2.51</t>
+  </si>
+  <si>
     <t xml:space="preserve">ПТОГ</t>
   </si>
   <si>
+    <t xml:space="preserve">Согл ПТО в год плане-графике</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Без него нельзя поставить ГИП.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2023 1100 1100877483; 2024 1100 1100884889; 2025 1100 1101878222</t>
   </si>
   <si>
     <t xml:space="preserve">ПТОМ</t>
   </si>
   <si>
+    <t xml:space="preserve">Согл ПТО в мес плане-графике</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Месячное оперативное планирование.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100319664; 2023 1100 1100877483; 2024 1100 1100884889</t>
   </si>
   <si>
     <t xml:space="preserve">ТКБЕ</t>
   </si>
   <si>
+    <t xml:space="preserve">Бюджет на год утвержден ТК БЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически из SAP MCB.</t>
+  </si>
+  <si>
     <t xml:space="preserve">УТВП</t>
   </si>
   <si>
+    <t xml:space="preserve">Утв в программе и бюджете</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически после утверждения программы и бюджета (из SAP MCB).</t>
+  </si>
+  <si>
     <t xml:space="preserve">СГЛБ</t>
   </si>
   <si>
+    <t xml:space="preserve">Согл спец по бюджетированию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согласовано специалистом по бюджетированию.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025 1100 1102140603; 2026 1100 1102226644; 2027 1100 1500033040</t>
   </si>
   <si>
     <t xml:space="preserve">ССПЛ</t>
   </si>
   <si>
+    <t xml:space="preserve">Согл Ст Пл ТОиР БЕ ГОК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Порядковый №3: согласовано старшим планировщиком; дальше заказ блокируется для изменений.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1500007834; 2023 1100 1500020529; 2024 1100 1500025393</t>
   </si>
   <si>
     <t xml:space="preserve">ФХСМ</t>
   </si>
   <si>
+    <t xml:space="preserve">Факт ХС, РП, МТР полн.проведен</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Техник подтверждает, что затрат больше не будет; заказ готов к ТЗКР.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">памятка ТОиР-84; скриншот окна статусов SAP (Статусы.docx)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025 1100 1200345311; 2024 1300 1101673514; 2025 1300 1101674364</t>
   </si>
   <si>
     <t xml:space="preserve">РИПР</t>
   </si>
   <si>
+    <t xml:space="preserve">Работы исполнены подрядчиком</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1200 2000038452; 2023 1200 2000046506; 2022 1400 1100592636</t>
   </si>
   <si>
-    <t xml:space="preserve">вывод по данным</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 1100 2100051692; 2027 1100 110000033568</t>
   </si>
   <si>
     <t xml:space="preserve">РЗПР</t>
   </si>
   <si>
+    <t xml:space="preserve">Работы запланир. подрядчиком</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1200109732; 2023 1100 1200152116; 2024 1100 1200260702</t>
   </si>
   <si>
     <t xml:space="preserve">ПЛАН</t>
   </si>
   <si>
+    <t xml:space="preserve">Планируется</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Порядковый №1: начальный статус, ставится автоматически.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100374749; 2023 1100 1101471084; 2024 1100 1101963158</t>
   </si>
   <si>
     <t xml:space="preserve">ПЛЗК</t>
   </si>
   <si>
+    <t xml:space="preserve">Плановый заказ</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100770856; 2023 1100 1100768199; 2024 1100 1101813707</t>
   </si>
   <si>
     <t xml:space="preserve">КОРБ</t>
   </si>
   <si>
+    <t xml:space="preserve">Бюджет выделен и скорректир-н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически по отдельному запросу.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100770915; 2023 1100 1100804673; 2024 1100 1101447598</t>
   </si>
   <si>
     <t xml:space="preserve">КРМТ</t>
   </si>
   <si>
+    <t xml:space="preserve">Капитализируемый ремонт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подпадает под критерии капитализации (CAPEX).</t>
+  </si>
+  <si>
     <t xml:space="preserve">ПЗТМ</t>
   </si>
   <si>
+    <t xml:space="preserve">Прогноз завершения месяца</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Воздействие согласовано в прогнозе завершения текущего месяца (срез КТГ).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">памятка ТОиР-66; скриншот окна статусов SAP (Статусы.docx)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1101012151; 2024 1100 1101259207</t>
   </si>
   <si>
     <t xml:space="preserve">МТРН</t>
   </si>
   <si>
+    <t xml:space="preserve">Материалы не оценены</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически: есть МТР без плановой цены.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100384609; 2023 1100 1101013018; 2024 1100 1101813707</t>
   </si>
   <si>
     <t xml:space="preserve">НВСО</t>
   </si>
   <si>
+    <t xml:space="preserve">Невостребованные остатки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Некорректируемый: ставится, когда удаляют законтрактованную потребность или закрывают заказ через ТЗКР, а материал уже закуплен.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">памятки ТОиР-75, ТОиР-96</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100375001; 2023 1100 1900003604; 2024 1100 1100884889</t>
   </si>
   <si>
     <t xml:space="preserve">СГПЛ</t>
   </si>
   <si>
+    <t xml:space="preserve">Отпр на согл Пл ТОиР БЕ ГОК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Порядковый №2: планировщик отправил заказ на согласование старшему планировщику.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1200128633; 2023 1100 1900003582; 2024 1100 1101267001</t>
   </si>
   <si>
     <t xml:space="preserve">ЗАПЛ</t>
   </si>
   <si>
+    <t xml:space="preserve">Запланирован</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Начальный статус схемы PM_ETO (ежесменное ТО).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19 табл. 23</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1600127329; 2025 1100 1600682946; 2026 1100 1600871206</t>
   </si>
   <si>
     <t xml:space="preserve">ТОПЗ</t>
   </si>
   <si>
+    <t xml:space="preserve">Требуется опереж. закуп</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нужна опережающая закупка.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026 1100 1101805027; 2027 1100 1102039908; 2026 1300 1102373845</t>
   </si>
   <si>
     <t xml:space="preserve">ПРЭК</t>
   </si>
   <si>
+    <t xml:space="preserve">Принято эксплуатацией</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Приёмка подразделением эксплуатации.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1200085136; 2023 1100 1100798987; 2024 1100 1101195035</t>
   </si>
   <si>
     <t xml:space="preserve">НДСГ</t>
   </si>
   <si>
+    <t xml:space="preserve">Наряд-допуск согласован</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100386576; 2023 1100 1200144892; 2024 1100 1101259258</t>
   </si>
   <si>
     <t xml:space="preserve">СОПЗ</t>
   </si>
   <si>
+    <t xml:space="preserve">Согласован опереж. закуп</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Опережающая закупка согласована.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2027 1100 1102536315</t>
   </si>
   <si>
     <t xml:space="preserve">ПОЛН</t>
   </si>
   <si>
+    <t xml:space="preserve">Заказ наполнен вручную</t>
+  </si>
+  <si>
     <t xml:space="preserve">ОЦЕН</t>
   </si>
   <si>
+    <t xml:space="preserve">Только сетевые графики P030. Расшифровки нет.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ТРКБ</t>
   </si>
   <si>
+    <t xml:space="preserve">Требуется коррект-ка бюджета</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Не хватает бюджета.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024 1100 1101350102; 2026 1100 1200469833; 2027 1400 1800018121</t>
   </si>
   <si>
     <t xml:space="preserve">КОРР</t>
   </si>
   <si>
+    <t xml:space="preserve">Требует корректировки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">По листу замечаний; снимается после исправления.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100374749; 2023 1100 1100813704; 2024 1100 1500021284</t>
   </si>
   <si>
     <t xml:space="preserve">МПРО</t>
   </si>
   <si>
+    <t xml:space="preserve">Планир-е ОстРемонта выполнено</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025 1100 1101831744; 2026 1100 1102077093; 2022 1200 1100362415</t>
   </si>
   <si>
     <t xml:space="preserve">ОСТ</t>
   </si>
   <si>
+    <t xml:space="preserve">Утвержден в графике ОстРемонта</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100455986; 2023 1100 1100820844; 2024 1100 1101371043</t>
   </si>
   <si>
     <t xml:space="preserve">МПРП</t>
   </si>
   <si>
+    <t xml:space="preserve">Планир-е ОстРемонт согласовано</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025 1100 1101831744; 2026 1100 1102077093; 2023 1300 1200166682</t>
   </si>
   <si>
     <t xml:space="preserve">УТВР</t>
   </si>
   <si>
+    <t xml:space="preserve">Утверждено (на ИК УК)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Статус заявки на замену оборудования (ОВП, вид P310), а не заказа ТОРО.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.73 «Планирование и согласование ОВП»</t>
+  </si>
+  <si>
     <t xml:space="preserve">2023 1300 4000033438; 2022 1400 4000018641</t>
   </si>
   <si>
     <t xml:space="preserve">ОТКБ</t>
   </si>
   <si>
+    <t xml:space="preserve">Коррект-ка бюджета отклонена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100420579; 2023 1100 1100824912; 2024 1100 1101967998</t>
   </si>
   <si>
     <t xml:space="preserve">СИНХ</t>
   </si>
   <si>
+    <t xml:space="preserve">Заказы синхронизированы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Со смежными службами.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2023 1400 1101038173; 2024 1400 1100825565</t>
   </si>
   <si>
     <t xml:space="preserve">МТПЛ</t>
   </si>
   <si>
+    <t xml:space="preserve">Материалы запланированы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Старая схема статусов (встречается только в 2022 году).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">документация (2 упоминания)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1001920</t>
   </si>
   <si>
     <t xml:space="preserve">МНБЛ</t>
   </si>
   <si>
+    <t xml:space="preserve">Мощности сбалансированы</t>
+  </si>
+  <si>
     <t xml:space="preserve">ПУСТ</t>
   </si>
   <si>
+    <t xml:space="preserve">Заказ треб ДопНаполн СоздБезТК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Создан без техкарты, требует наполнения.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2023 1100 1100804148; 2024 1100 1101374664; 2025 1100 1101480814</t>
   </si>
   <si>
     <t xml:space="preserve">ТЛИМ</t>
   </si>
   <si>
+    <t xml:space="preserve">Техлимит</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025 1100 1900004243; 2026 1100 1102260065; 2025 1400 1101645185</t>
   </si>
   <si>
     <t xml:space="preserve">МАТП</t>
   </si>
   <si>
+    <t xml:space="preserve">Материалы подтверждены</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Замечаний нет.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024 1200 1101478938</t>
   </si>
   <si>
     <t xml:space="preserve">ИНИЦ</t>
   </si>
   <si>
+    <t xml:space="preserve">Инициатива</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 4000009964</t>
   </si>
   <si>
     <t xml:space="preserve">НПРН</t>
   </si>
   <si>
+    <t xml:space="preserve">Работы не приняты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нужно повторное планирование; блокирует ТЗКР.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024 1100 910100042800; 2022 1200 1100369371; 2023 1200 1200154647</t>
   </si>
   <si>
     <t xml:space="preserve">ДФКТ</t>
   </si>
   <si>
+    <t xml:space="preserve">ДефВедомость сформирована</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1400 1200104757</t>
   </si>
   <si>
     <t xml:space="preserve">РСЦН</t>
   </si>
   <si>
+    <t xml:space="preserve">Расценено</t>
+  </si>
+  <si>
     <t xml:space="preserve">2023 1300 4000033438; 2022 1400 4000018234</t>
   </si>
   <si>
     <t xml:space="preserve">СПКИ</t>
   </si>
   <si>
+    <t xml:space="preserve">Согласовано ОПиКИ</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1400 4000018477</t>
   </si>
   <si>
     <t xml:space="preserve">ИСПП</t>
   </si>
   <si>
+    <t xml:space="preserve">Исполнители запланированы</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100375033; 2024 1100 1101932625; 2023 1200 1100775695</t>
   </si>
   <si>
+    <t xml:space="preserve">Нет материалов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При выявлении недоступности МТР.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1400 1100592900</t>
   </si>
   <si>
     <t xml:space="preserve">АСКИ</t>
   </si>
   <si>
+    <t xml:space="preserve">Заявка согласована в АСКИ</t>
+  </si>
+  <si>
     <t xml:space="preserve">2023 1300 4000033438</t>
   </si>
   <si>
     <t xml:space="preserve">ИНВС</t>
   </si>
   <si>
+    <t xml:space="preserve">Реализация как инвест. проект</t>
+  </si>
+  <si>
     <t xml:space="preserve">МПРА</t>
   </si>
   <si>
+    <t xml:space="preserve">Авт планир ОстРемонт выполнено</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1101031340; 2023 1100 1200166084</t>
   </si>
   <si>
     <t xml:space="preserve">МТРП</t>
   </si>
   <si>
+    <t xml:space="preserve">Планировщик закончил планирование МТР.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2023 1300 1200181126; 2022 1400 1200093705</t>
   </si>
   <si>
     <t xml:space="preserve">ПРОВ</t>
   </si>
   <si>
+    <t xml:space="preserve">Заказ проверен Ст. Планиров-ом</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100596675</t>
   </si>
   <si>
     <t xml:space="preserve">ОСМЧ</t>
   </si>
   <si>
+    <t xml:space="preserve">Осмечен</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Внесены плановые стоимости из сметы.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1100 1100456519</t>
   </si>
   <si>
     <t xml:space="preserve">ВПСС</t>
   </si>
   <si>
+    <t xml:space="preserve">ВПС сбаланс со смежн заказами</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 1400 1100589992</t>
   </si>
   <si>
     <t xml:space="preserve">МТРЗ</t>
   </si>
   <si>
+    <t xml:space="preserve">Материалы заменены</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На более целесообразные.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026 1400 1102206103</t>
   </si>
   <si>
@@ -846,9 +1311,6 @@
   </si>
   <si>
     <t xml:space="preserve">Всего</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нет статуса</t>
   </si>
 </sst>
 </file>
@@ -861,7 +1323,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;\-0.0%;\-"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;\-#,##0.0;\-"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -907,6 +1369,14 @@
     <font>
       <i val="true"/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -988,7 +1458,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1045,11 +1515,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1078,7 +1552,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1097,6 +1571,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -1107,7 +1589,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1354,7 +1836,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -1408,82 +1890,85 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="5" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-    </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1503,7 +1988,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:X39"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="9"/>
@@ -1511,18 +1996,19 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="12" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>26</v>
@@ -1570,7 +2056,7 @@
         <v>40</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R1" s="7" t="s">
         <v>41</v>
@@ -1581,8 +2067,8 @@
       <c r="T1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="U1" s="8" t="s">
-        <v>11</v>
+      <c r="U1" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="V1" s="8" t="s">
         <v>12</v>
@@ -1590,10 +2076,13 @@
       <c r="W1" s="8" t="s">
         <v>13</v>
       </c>
+      <c r="X1" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="10" t="n">
         <v>59275</v>
@@ -1642,20 +2131,25 @@
         <v>0</v>
       </c>
       <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
+      <c r="R2" s="13" t="s">
+        <v>46</v>
+      </c>
       <c r="S2" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T2" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U2" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B3" s="10" t="n">
         <v>59274</v>
@@ -1704,24 +2198,27 @@
         <v>0</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="R3" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="U3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="S3" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="T3" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B4" s="10" t="n">
         <v>58789</v>
@@ -1770,24 +2267,27 @@
         <v>0</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="R4" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="S4" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="T4" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U4" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B5" s="10" t="n">
         <v>58775</v>
@@ -1836,24 +2336,27 @@
         <v>0</v>
       </c>
       <c r="Q5" s="13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="R5" s="13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="S5" s="13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="T5" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U5" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>58340</v>
@@ -1901,21 +2404,28 @@
       <c r="P6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
+      <c r="Q6" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="S6" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T6" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>64</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="U6" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>58470</v>
@@ -1964,24 +2474,27 @@
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="R7" s="13" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="S7" s="13" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U7" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>46266</v>
@@ -2029,25 +2542,26 @@
       <c r="P8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="13" t="s">
-        <v>61</v>
-      </c>
+      <c r="Q8" s="13"/>
       <c r="R8" s="13" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="S8" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="T8" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+        <v>72</v>
+      </c>
+      <c r="T8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="U8" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V8" s="15"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B9" s="10" t="n">
         <v>43887</v>
@@ -2096,24 +2610,27 @@
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="S9" s="13" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B10" s="10" t="n">
         <v>0</v>
@@ -2161,21 +2678,28 @@
       <c r="P10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
+      <c r="Q10" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>81</v>
+      </c>
       <c r="S10" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T10" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
+        <v>64</v>
+      </c>
+      <c r="T10" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="U10" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B11" s="10" t="n">
         <v>0</v>
@@ -2223,21 +2747,28 @@
       <c r="P11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
+      <c r="Q11" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="R11" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="S11" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T11" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="U11" s="14"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
+        <v>87</v>
+      </c>
+      <c r="T11" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="U11" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="V11" s="15"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B12" s="10" t="n">
         <v>0</v>
@@ -2286,20 +2817,25 @@
         <v>0</v>
       </c>
       <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
+      <c r="R12" s="13" t="s">
+        <v>90</v>
+      </c>
       <c r="S12" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T12" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="U12" s="14"/>
-      <c r="V12" s="14"/>
-      <c r="W12" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T12" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U12" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="V12" s="15"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B13" s="10" t="n">
         <v>14724</v>
@@ -2348,24 +2884,27 @@
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="S13" s="13" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="T13" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U13" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="V13" s="13"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>6213</v>
@@ -2413,21 +2952,28 @@
       <c r="P14" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
+      <c r="Q14" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R14" s="13" t="s">
+        <v>97</v>
+      </c>
       <c r="S14" s="13" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U14" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>23</v>
@@ -2476,24 +3022,27 @@
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="R15" s="13" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="S15" s="13" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="T15" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U15" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="B16" s="10" t="n">
         <v>2897</v>
@@ -2542,24 +3091,27 @@
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="S16" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="T16" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="U16" s="14"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
+        <v>106</v>
+      </c>
+      <c r="T16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="U16" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="V16" s="15"/>
+      <c r="W16" s="15"/>
+      <c r="X16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B17" s="10" t="n">
         <v>2588</v>
@@ -2608,24 +3160,27 @@
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="S17" s="13" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="T17" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U17" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="B18" s="10" t="n">
         <v>6715</v>
@@ -2673,21 +3228,28 @@
       <c r="P18" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
+      <c r="Q18" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="R18" s="13" t="s">
+        <v>114</v>
+      </c>
       <c r="S18" s="13" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="T18" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="14"/>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U18" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+    </row>
+    <row r="19" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>307</v>
@@ -2736,24 +3298,27 @@
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="S19" s="13" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="T19" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U19" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="B20" s="10" t="n">
         <v>0</v>
@@ -2802,24 +3367,27 @@
         <v>1</v>
       </c>
       <c r="Q20" s="13" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="R20" s="13" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="S20" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="T20" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
+        <v>125</v>
+      </c>
+      <c r="T20" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="U20" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="V20" s="15"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="B21" s="10" t="n">
         <v>2102</v>
@@ -2868,20 +3436,25 @@
         <v>0</v>
       </c>
       <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
+      <c r="R21" s="13" t="s">
+        <v>128</v>
+      </c>
       <c r="S21" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T21" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+      <c r="T21" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U21" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>469</v>
@@ -2930,24 +3503,27 @@
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="R22" s="13" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="T22" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U22" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="V22" s="13"/>
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>0</v>
@@ -2996,20 +3572,25 @@
         <v>0</v>
       </c>
       <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
+      <c r="R23" s="13" t="s">
+        <v>135</v>
+      </c>
       <c r="S23" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T23" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T23" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U23" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>556</v>
@@ -3058,20 +3639,25 @@
         <v>0</v>
       </c>
       <c r="Q24" s="13"/>
-      <c r="R24" s="13"/>
+      <c r="R24" s="13" t="s">
+        <v>138</v>
+      </c>
       <c r="S24" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T24" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T24" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="U24" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>875</v>
@@ -3120,20 +3706,25 @@
         <v>0</v>
       </c>
       <c r="Q25" s="13"/>
-      <c r="R25" s="13"/>
+      <c r="R25" s="13" t="s">
+        <v>142</v>
+      </c>
       <c r="S25" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T25" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T25" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U25" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V25" s="15"/>
+      <c r="W25" s="15"/>
+      <c r="X25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>499</v>
@@ -3182,20 +3773,25 @@
         <v>0</v>
       </c>
       <c r="Q26" s="13"/>
-      <c r="R26" s="13"/>
+      <c r="R26" s="13" t="s">
+        <v>144</v>
+      </c>
       <c r="S26" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T26" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T26" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U26" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="B27" s="10" t="n">
         <v>439</v>
@@ -3244,20 +3840,25 @@
         <v>0</v>
       </c>
       <c r="Q27" s="13"/>
-      <c r="R27" s="13"/>
+      <c r="R27" s="13" t="s">
+        <v>146</v>
+      </c>
       <c r="S27" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T27" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="U27" s="14"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T27" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U27" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="B28" s="10" t="n">
         <v>48</v>
@@ -3305,25 +3906,26 @@
       <c r="P28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" s="13" t="s">
-        <v>114</v>
-      </c>
+      <c r="Q28" s="13"/>
       <c r="R28" s="13" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="T28" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="U28" s="14"/>
-      <c r="V28" s="14"/>
-      <c r="W28" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T28" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U28" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="V28" s="15"/>
+      <c r="W28" s="15"/>
+      <c r="X28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="B29" s="10" t="n">
         <v>298</v>
@@ -3372,20 +3974,25 @@
         <v>0</v>
       </c>
       <c r="Q29" s="13"/>
-      <c r="R29" s="13"/>
+      <c r="R29" s="13" t="s">
+        <v>152</v>
+      </c>
       <c r="S29" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T29" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="U29" s="14"/>
-      <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
+        <v>72</v>
+      </c>
+      <c r="T29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="U29" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="V29" s="15"/>
+      <c r="W29" s="15"/>
+      <c r="X29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="B30" s="10" t="n">
         <v>292</v>
@@ -3434,20 +4041,25 @@
         <v>0</v>
       </c>
       <c r="Q30" s="13"/>
-      <c r="R30" s="13"/>
+      <c r="R30" s="13" t="s">
+        <v>155</v>
+      </c>
       <c r="S30" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T30" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T30" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U30" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="V30" s="15"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="15"/>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="B31" s="10" t="n">
         <v>292</v>
@@ -3496,20 +4108,25 @@
         <v>0</v>
       </c>
       <c r="Q31" s="13"/>
-      <c r="R31" s="13"/>
+      <c r="R31" s="13" t="s">
+        <v>155</v>
+      </c>
       <c r="S31" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T31" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="U31" s="14"/>
-      <c r="V31" s="14"/>
-      <c r="W31" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T31" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U31" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="V31" s="15"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="B32" s="10" t="n">
         <v>292</v>
@@ -3558,20 +4175,25 @@
         <v>0</v>
       </c>
       <c r="Q32" s="13"/>
-      <c r="R32" s="13"/>
+      <c r="R32" s="13" t="s">
+        <v>155</v>
+      </c>
       <c r="S32" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T32" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="U32" s="14"/>
-      <c r="V32" s="14"/>
-      <c r="W32" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T32" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U32" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="V32" s="15"/>
+      <c r="W32" s="15"/>
+      <c r="X32" s="15"/>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="B33" s="10" t="n">
         <v>6</v>
@@ -3620,24 +4242,27 @@
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="R33" s="13" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="S33" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="T33" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="U33" s="14"/>
-      <c r="V33" s="14"/>
-      <c r="W33" s="14"/>
+        <v>72</v>
+      </c>
+      <c r="T33" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="U33" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="V33" s="15"/>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="B34" s="10" t="n">
         <v>0</v>
@@ -3686,20 +4311,25 @@
         <v>0</v>
       </c>
       <c r="Q34" s="13"/>
-      <c r="R34" s="13"/>
+      <c r="R34" s="13" t="s">
+        <v>163</v>
+      </c>
       <c r="S34" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T34" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="U34" s="14"/>
-      <c r="V34" s="14"/>
-      <c r="W34" s="14"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+      <c r="T34" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U34" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="V34" s="15"/>
+      <c r="W34" s="15"/>
+      <c r="X34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="B35" s="10" t="n">
         <v>20</v>
@@ -3747,21 +4377,28 @@
       <c r="P35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
+      <c r="Q35" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="R35" s="13" t="s">
+        <v>167</v>
+      </c>
       <c r="S35" s="13" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="T35" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="U35" s="14"/>
-      <c r="V35" s="14"/>
-      <c r="W35" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U35" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="B36" s="10" t="n">
         <v>7</v>
@@ -3810,20 +4447,25 @@
         <v>0</v>
       </c>
       <c r="Q36" s="13"/>
-      <c r="R36" s="13"/>
+      <c r="R36" s="13" t="s">
+        <v>170</v>
+      </c>
       <c r="S36" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T36" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="U36" s="14"/>
-      <c r="V36" s="14"/>
-      <c r="W36" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T36" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U36" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="V36" s="15"/>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="B37" s="10" t="n">
         <v>5</v>
@@ -3872,20 +4514,25 @@
         <v>0</v>
       </c>
       <c r="Q37" s="13"/>
-      <c r="R37" s="13"/>
+      <c r="R37" s="13" t="s">
+        <v>173</v>
+      </c>
       <c r="S37" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T37" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T37" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U37" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="V37" s="15"/>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="B38" s="10" t="n">
         <v>2</v>
@@ -3934,20 +4581,25 @@
         <v>0</v>
       </c>
       <c r="Q38" s="13"/>
-      <c r="R38" s="13"/>
+      <c r="R38" s="13" t="s">
+        <v>176</v>
+      </c>
       <c r="S38" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T38" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="U38" s="14"/>
-      <c r="V38" s="14"/>
-      <c r="W38" s="14"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+      <c r="T38" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U38" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="V38" s="15"/>
+      <c r="W38" s="15"/>
+      <c r="X38" s="15"/>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="B39" s="10" t="n">
         <v>2</v>
@@ -3996,23 +4648,26 @@
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="R39" s="13" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="S39" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="T39" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="U39" s="14"/>
-      <c r="V39" s="14"/>
-      <c r="W39" s="14"/>
+        <v>106</v>
+      </c>
+      <c r="T39" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="U39" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="V39" s="15"/>
+      <c r="W39" s="15"/>
+      <c r="X39" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W39"/>
+  <autoFilter ref="A1:X39"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4029,7 +4684,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W68"/>
+  <dimension ref="A1:X68"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="9"/>
@@ -4037,18 +4692,19 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="12" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>26</v>
@@ -4096,7 +4752,7 @@
         <v>40</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R1" s="7" t="s">
         <v>41</v>
@@ -4107,8 +4763,8 @@
       <c r="T1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="U1" s="8" t="s">
-        <v>11</v>
+      <c r="U1" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="V1" s="8" t="s">
         <v>12</v>
@@ -4116,10 +4772,13 @@
       <c r="W1" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="X1" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="B2" s="10" t="n">
         <v>52170</v>
@@ -4167,21 +4826,28 @@
       <c r="P2" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
+      <c r="Q2" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>184</v>
+      </c>
       <c r="S2" s="13" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="T2" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U2" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="B3" s="10" t="n">
         <v>51506</v>
@@ -4229,21 +4895,28 @@
       <c r="P3" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
+      <c r="Q3" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>187</v>
+      </c>
       <c r="S3" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="B4" s="10" t="n">
         <v>26998</v>
@@ -4292,24 +4965,27 @@
         <v>0</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>58</v>
+        <v>191</v>
       </c>
       <c r="S4" s="13" t="s">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U4" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="B5" s="10" t="n">
         <v>15159</v>
@@ -4357,21 +5033,28 @@
       <c r="P5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
+      <c r="Q5" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>195</v>
+      </c>
       <c r="S5" s="13" t="s">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="T5" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U5" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>25540</v>
@@ -4419,21 +5102,28 @@
       <c r="P6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
+      <c r="Q6" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>200</v>
+      </c>
       <c r="S6" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U6" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>148</v>
+        <v>201</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>0</v>
@@ -4481,21 +5171,28 @@
       <c r="P7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
+      <c r="Q7" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>203</v>
+      </c>
       <c r="S7" s="13" t="s">
-        <v>45</v>
+        <v>204</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U7" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>0</v>
@@ -4543,21 +5240,28 @@
       <c r="P8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
+      <c r="Q8" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="R8" s="13" t="s">
+        <v>207</v>
+      </c>
       <c r="S8" s="13" t="s">
-        <v>45</v>
+        <v>208</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U8" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>150</v>
+        <v>209</v>
       </c>
       <c r="B9" s="10" t="n">
         <v>18655</v>
@@ -4605,21 +5309,28 @@
       <c r="P9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
+      <c r="Q9" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>211</v>
+      </c>
       <c r="S9" s="13" t="s">
-        <v>45</v>
+        <v>212</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="B10" s="10" t="n">
         <v>15149</v>
@@ -4668,24 +5379,27 @@
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="R10" s="13" t="s">
-        <v>58</v>
+        <v>215</v>
       </c>
       <c r="S10" s="13" t="s">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="T10" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U10" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="B11" s="10" t="n">
         <v>21688</v>
@@ -4734,24 +5448,27 @@
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>155</v>
+        <v>218</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="S11" s="13" t="s">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="T11" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="U11" s="14"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U11" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>157</v>
+        <v>221</v>
       </c>
       <c r="B12" s="10" t="n">
         <v>20618</v>
@@ -4800,24 +5517,27 @@
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="s">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="R12" s="13" t="s">
-        <v>58</v>
+        <v>223</v>
       </c>
       <c r="S12" s="13" t="s">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="T12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="U12" s="14"/>
-      <c r="V12" s="14"/>
-      <c r="W12" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U12" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>159</v>
+        <v>224</v>
       </c>
       <c r="B13" s="10" t="n">
         <v>23580</v>
@@ -4866,24 +5586,27 @@
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>58</v>
+        <v>223</v>
       </c>
       <c r="S13" s="13" t="s">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="T13" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U13" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="V13" s="13"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>161</v>
+        <v>226</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>18365</v>
@@ -4932,24 +5655,27 @@
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="s">
-        <v>162</v>
+        <v>227</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="S14" s="13" t="s">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U14" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>19235</v>
@@ -4997,21 +5723,28 @@
       <c r="P15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
+      <c r="Q15" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>231</v>
+      </c>
       <c r="S15" s="13" t="s">
-        <v>45</v>
+        <v>232</v>
       </c>
       <c r="T15" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U15" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="B16" s="10" t="n">
         <v>4387</v>
@@ -5059,21 +5792,28 @@
       <c r="P16" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
+      <c r="Q16" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="R16" s="13" t="s">
+        <v>235</v>
+      </c>
       <c r="S16" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T16" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="U16" s="14"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U16" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="V16" s="13"/>
+      <c r="W16" s="13"/>
+      <c r="X16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>167</v>
+        <v>237</v>
       </c>
       <c r="B17" s="10" t="n">
         <v>5847</v>
@@ -5121,21 +5861,28 @@
       <c r="P17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
+      <c r="Q17" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="R17" s="13" t="s">
+        <v>239</v>
+      </c>
       <c r="S17" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T17" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U17" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>169</v>
+        <v>241</v>
       </c>
       <c r="B18" s="10" t="n">
         <v>13027</v>
@@ -5183,21 +5930,28 @@
       <c r="P18" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
+      <c r="Q18" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="R18" s="13" t="s">
+        <v>243</v>
+      </c>
       <c r="S18" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T18" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U18" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>170</v>
+        <v>244</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>11151</v>
@@ -5245,21 +5999,28 @@
       <c r="P19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
+      <c r="Q19" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="R19" s="13" t="s">
+        <v>246</v>
+      </c>
       <c r="S19" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T19" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U19" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>171</v>
+        <v>247</v>
       </c>
       <c r="B20" s="10" t="n">
         <v>0</v>
@@ -5307,21 +6068,28 @@
       <c r="P20" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
+      <c r="Q20" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="R20" s="13" t="s">
+        <v>249</v>
+      </c>
       <c r="S20" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T20" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>87</v>
+      </c>
+      <c r="T20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="U20" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="V20" s="15"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>173</v>
+        <v>251</v>
       </c>
       <c r="B21" s="10" t="n">
         <v>4095</v>
@@ -5369,21 +6137,28 @@
       <c r="P21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
+      <c r="Q21" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="R21" s="13" t="s">
+        <v>253</v>
+      </c>
       <c r="S21" s="13" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="T21" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U21" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="V21" s="13"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>175</v>
+        <v>255</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>0</v>
@@ -5431,21 +6206,28 @@
       <c r="P22" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="13"/>
+      <c r="Q22" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="R22" s="13" t="s">
+        <v>257</v>
+      </c>
       <c r="S22" s="13" t="s">
-        <v>45</v>
+        <v>258</v>
       </c>
       <c r="T22" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U22" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="V22" s="13"/>
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>177</v>
+        <v>260</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>7194</v>
@@ -5493,21 +6275,26 @@
       <c r="P23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="13"/>
+      <c r="Q23" s="13" t="s">
+        <v>261</v>
+      </c>
       <c r="R23" s="13"/>
       <c r="S23" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T23" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>87</v>
+      </c>
+      <c r="T23" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="U23" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>0</v>
@@ -5556,24 +6343,27 @@
         <v>1</v>
       </c>
       <c r="Q24" s="13" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="R24" s="13" t="s">
-        <v>179</v>
+        <v>124</v>
       </c>
       <c r="S24" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="T24" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
+        <v>125</v>
+      </c>
+      <c r="T24" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="U24" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>181</v>
+        <v>264</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>6355</v>
@@ -5621,21 +6411,26 @@
       <c r="P25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="13"/>
+      <c r="Q25" s="13" t="s">
+        <v>265</v>
+      </c>
       <c r="R25" s="13"/>
       <c r="S25" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T25" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>87</v>
+      </c>
+      <c r="T25" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="U25" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="V25" s="15"/>
+      <c r="W25" s="15"/>
+      <c r="X25" s="15"/>
+    </row>
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>183</v>
+        <v>267</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>24</v>
@@ -5683,21 +6478,28 @@
       <c r="P26" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="13"/>
+      <c r="Q26" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>269</v>
+      </c>
       <c r="S26" s="13" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="T26" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U26" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>185</v>
+        <v>271</v>
       </c>
       <c r="B27" s="10" t="n">
         <v>946</v>
@@ -5745,21 +6547,26 @@
       <c r="P27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" s="13"/>
+      <c r="Q27" s="13" t="s">
+        <v>272</v>
+      </c>
       <c r="R27" s="13"/>
       <c r="S27" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T27" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="U27" s="14"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="14"/>
+        <v>87</v>
+      </c>
+      <c r="T27" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="U27" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>187</v>
+        <v>274</v>
       </c>
       <c r="B28" s="10" t="n">
         <v>21</v>
@@ -5807,21 +6614,28 @@
       <c r="P28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="13"/>
+      <c r="Q28" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="R28" s="13" t="s">
+        <v>276</v>
+      </c>
       <c r="S28" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T28" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="U28" s="14"/>
-      <c r="V28" s="14"/>
-      <c r="W28" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U28" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>189</v>
+        <v>278</v>
       </c>
       <c r="B29" s="10" t="n">
         <v>875</v>
@@ -5869,21 +6683,28 @@
       <c r="P29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="13"/>
+      <c r="Q29" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="R29" s="13" t="s">
+        <v>280</v>
+      </c>
       <c r="S29" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T29" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="U29" s="14"/>
-      <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U29" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>190</v>
+        <v>281</v>
       </c>
       <c r="B30" s="10" t="n">
         <v>1316</v>
@@ -5931,21 +6752,28 @@
       <c r="P30" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="13"/>
-      <c r="R30" s="13"/>
+      <c r="Q30" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="R30" s="13" t="s">
+        <v>283</v>
+      </c>
       <c r="S30" s="13" t="s">
-        <v>45</v>
+        <v>284</v>
       </c>
       <c r="T30" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U30" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+      <c r="X30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>192</v>
+        <v>286</v>
       </c>
       <c r="B31" s="10" t="n">
         <v>306</v>
@@ -5993,21 +6821,28 @@
       <c r="P31" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="13"/>
-      <c r="R31" s="13"/>
+      <c r="Q31" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="R31" s="13" t="s">
+        <v>288</v>
+      </c>
       <c r="S31" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T31" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="U31" s="14"/>
-      <c r="V31" s="14"/>
-      <c r="W31" s="14"/>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U31" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="V31" s="13"/>
+      <c r="W31" s="13"/>
+      <c r="X31" s="13"/>
+    </row>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>194</v>
+        <v>290</v>
       </c>
       <c r="B32" s="10" t="n">
         <v>2</v>
@@ -6055,21 +6890,28 @@
       <c r="P32" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="13"/>
-      <c r="R32" s="13"/>
+      <c r="Q32" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="R32" s="13" t="s">
+        <v>292</v>
+      </c>
       <c r="S32" s="13" t="s">
-        <v>45</v>
+        <v>293</v>
       </c>
       <c r="T32" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="U32" s="14"/>
-      <c r="V32" s="14"/>
-      <c r="W32" s="14"/>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U32" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="V32" s="13"/>
+      <c r="W32" s="13"/>
+      <c r="X32" s="13"/>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>196</v>
+        <v>295</v>
       </c>
       <c r="B33" s="10" t="n">
         <v>636</v>
@@ -6117,21 +6959,28 @@
       <c r="P33" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="13"/>
-      <c r="R33" s="13"/>
+      <c r="Q33" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="R33" s="13" t="s">
+        <v>297</v>
+      </c>
       <c r="S33" s="13" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="T33" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="U33" s="14"/>
-      <c r="V33" s="14"/>
-      <c r="W33" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U33" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="V33" s="13"/>
+      <c r="W33" s="13"/>
+      <c r="X33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>198</v>
+        <v>299</v>
       </c>
       <c r="B34" s="10" t="n">
         <v>1563</v>
@@ -6179,21 +7028,28 @@
       <c r="P34" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" s="13"/>
-      <c r="R34" s="13"/>
+      <c r="Q34" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="R34" s="13" t="s">
+        <v>301</v>
+      </c>
       <c r="S34" s="13" t="s">
-        <v>45</v>
+        <v>302</v>
       </c>
       <c r="T34" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="U34" s="14"/>
-      <c r="V34" s="14"/>
-      <c r="W34" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U34" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="V34" s="13"/>
+      <c r="W34" s="13"/>
+      <c r="X34" s="13"/>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>200</v>
+        <v>304</v>
       </c>
       <c r="B35" s="10" t="n">
         <v>0</v>
@@ -6241,21 +7097,28 @@
       <c r="P35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
+      <c r="Q35" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="R35" s="13" t="s">
+        <v>306</v>
+      </c>
       <c r="S35" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T35" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="U35" s="14"/>
-      <c r="V35" s="14"/>
-      <c r="W35" s="14"/>
+        <v>87</v>
+      </c>
+      <c r="T35" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="U35" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="V35" s="15"/>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="B36" s="10" t="n">
         <v>346</v>
@@ -6303,21 +7166,28 @@
       <c r="P36" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" s="13"/>
-      <c r="R36" s="13"/>
+      <c r="Q36" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="R36" s="13" t="s">
+        <v>310</v>
+      </c>
       <c r="S36" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T36" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="U36" s="14"/>
-      <c r="V36" s="14"/>
-      <c r="W36" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U36" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>204</v>
+        <v>312</v>
       </c>
       <c r="B37" s="10" t="n">
         <v>238</v>
@@ -6365,21 +7235,26 @@
       <c r="P37" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" s="13"/>
+      <c r="Q37" s="13" t="s">
+        <v>313</v>
+      </c>
       <c r="R37" s="13"/>
       <c r="S37" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T37" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U37" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>206</v>
+        <v>315</v>
       </c>
       <c r="B38" s="10" t="n">
         <v>0</v>
@@ -6427,21 +7302,28 @@
       <c r="P38" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" s="13"/>
-      <c r="R38" s="13"/>
+      <c r="Q38" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="R38" s="13" t="s">
+        <v>317</v>
+      </c>
       <c r="S38" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T38" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="U38" s="14"/>
-      <c r="V38" s="14"/>
-      <c r="W38" s="14"/>
+        <v>87</v>
+      </c>
+      <c r="T38" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="U38" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="V38" s="15"/>
+      <c r="W38" s="15"/>
+      <c r="X38" s="15"/>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>208</v>
+        <v>319</v>
       </c>
       <c r="B39" s="10" t="n">
         <v>205</v>
@@ -6489,21 +7371,26 @@
       <c r="P39" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" s="13"/>
+      <c r="Q39" s="13" t="s">
+        <v>320</v>
+      </c>
       <c r="R39" s="13"/>
       <c r="S39" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T39" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="U39" s="14"/>
-      <c r="V39" s="14"/>
-      <c r="W39" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U39" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>209</v>
+        <v>321</v>
       </c>
       <c r="B40" s="10" t="n">
         <v>55</v>
@@ -6552,20 +7439,25 @@
         <v>0</v>
       </c>
       <c r="Q40" s="13"/>
-      <c r="R40" s="13"/>
+      <c r="R40" s="13" t="s">
+        <v>322</v>
+      </c>
       <c r="S40" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T40" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="U40" s="14"/>
-      <c r="V40" s="14"/>
-      <c r="W40" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="T40" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U40" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="V40" s="15"/>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>210</v>
+        <v>323</v>
       </c>
       <c r="B41" s="10" t="n">
         <v>0</v>
@@ -6613,21 +7505,28 @@
       <c r="P41" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" s="13"/>
-      <c r="R41" s="13"/>
+      <c r="Q41" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="R41" s="13" t="s">
+        <v>325</v>
+      </c>
       <c r="S41" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T41" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="U41" s="14"/>
-      <c r="V41" s="14"/>
-      <c r="W41" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U41" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="V41" s="13"/>
+      <c r="W41" s="13"/>
+      <c r="X41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>212</v>
+        <v>327</v>
       </c>
       <c r="B42" s="10" t="n">
         <v>11</v>
@@ -6675,21 +7574,28 @@
       <c r="P42" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="13"/>
-      <c r="R42" s="13"/>
+      <c r="Q42" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="R42" s="13" t="s">
+        <v>329</v>
+      </c>
       <c r="S42" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T42" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="U42" s="14"/>
-      <c r="V42" s="14"/>
-      <c r="W42" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U42" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="V42" s="13"/>
+      <c r="W42" s="13"/>
+      <c r="X42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>214</v>
+        <v>331</v>
       </c>
       <c r="B43" s="10" t="n">
         <v>260</v>
@@ -6737,21 +7643,26 @@
       <c r="P43" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" s="13"/>
+      <c r="Q43" s="13" t="s">
+        <v>332</v>
+      </c>
       <c r="R43" s="13"/>
       <c r="S43" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T43" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="U43" s="14"/>
-      <c r="V43" s="14"/>
-      <c r="W43" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U43" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="V43" s="13"/>
+      <c r="W43" s="13"/>
+      <c r="X43" s="13"/>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>216</v>
+        <v>334</v>
       </c>
       <c r="B44" s="10" t="n">
         <v>178</v>
@@ -6799,21 +7710,26 @@
       <c r="P44" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" s="13"/>
+      <c r="Q44" s="13" t="s">
+        <v>335</v>
+      </c>
       <c r="R44" s="13"/>
       <c r="S44" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T44" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="U44" s="14"/>
-      <c r="V44" s="14"/>
-      <c r="W44" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U44" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="V44" s="13"/>
+      <c r="W44" s="13"/>
+      <c r="X44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>218</v>
+        <v>337</v>
       </c>
       <c r="B45" s="10" t="n">
         <v>257</v>
@@ -6861,21 +7777,26 @@
       <c r="P45" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" s="13"/>
+      <c r="Q45" s="13" t="s">
+        <v>338</v>
+      </c>
       <c r="R45" s="13"/>
       <c r="S45" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T45" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="U45" s="14"/>
-      <c r="V45" s="14"/>
-      <c r="W45" s="14"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U45" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="V45" s="13"/>
+      <c r="W45" s="13"/>
+      <c r="X45" s="13"/>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="B46" s="10" t="n">
         <v>408</v>
@@ -6923,21 +7844,28 @@
       <c r="P46" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" s="13"/>
-      <c r="R46" s="13"/>
+      <c r="Q46" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="R46" s="13" t="s">
+        <v>342</v>
+      </c>
       <c r="S46" s="13" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
       <c r="T46" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="U46" s="14"/>
-      <c r="V46" s="14"/>
-      <c r="W46" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U46" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="V46" s="13"/>
+      <c r="W46" s="13"/>
+      <c r="X46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>222</v>
+        <v>345</v>
       </c>
       <c r="B47" s="10" t="n">
         <v>3</v>
@@ -6985,21 +7913,28 @@
       <c r="P47" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" s="13"/>
-      <c r="R47" s="13"/>
+      <c r="Q47" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="R47" s="13" t="s">
+        <v>347</v>
+      </c>
       <c r="S47" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T47" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="U47" s="14"/>
-      <c r="V47" s="14"/>
-      <c r="W47" s="14"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U47" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="V47" s="13"/>
+      <c r="W47" s="13"/>
+      <c r="X47" s="13"/>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>224</v>
+        <v>349</v>
       </c>
       <c r="B48" s="10" t="n">
         <v>0</v>
@@ -7047,21 +7982,28 @@
       <c r="P48" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" s="13"/>
-      <c r="R48" s="13"/>
+      <c r="Q48" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="R48" s="13" t="s">
+        <v>351</v>
+      </c>
       <c r="S48" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T48" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="U48" s="14"/>
-      <c r="V48" s="14"/>
-      <c r="W48" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U48" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="V48" s="13"/>
+      <c r="W48" s="13"/>
+      <c r="X48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
-        <v>226</v>
+        <v>353</v>
       </c>
       <c r="B49" s="10" t="n">
         <v>47</v>
@@ -7109,21 +8051,28 @@
       <c r="P49" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" s="13"/>
-      <c r="R49" s="13"/>
+      <c r="Q49" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="R49" s="13" t="s">
+        <v>355</v>
+      </c>
       <c r="S49" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T49" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="U49" s="14"/>
-      <c r="V49" s="14"/>
-      <c r="W49" s="14"/>
+        <v>356</v>
+      </c>
+      <c r="T49" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="U49" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="V49" s="15"/>
+      <c r="W49" s="15"/>
+      <c r="X49" s="15"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="B50" s="10" t="n">
         <v>47</v>
@@ -7171,21 +8120,28 @@
       <c r="P50" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" s="13"/>
-      <c r="R50" s="13"/>
+      <c r="Q50" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="R50" s="13" t="s">
+        <v>355</v>
+      </c>
       <c r="S50" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T50" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="U50" s="14"/>
-      <c r="V50" s="14"/>
-      <c r="W50" s="14"/>
+        <v>356</v>
+      </c>
+      <c r="T50" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="U50" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="V50" s="15"/>
+      <c r="W50" s="15"/>
+      <c r="X50" s="15"/>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>229</v>
+        <v>360</v>
       </c>
       <c r="B51" s="10" t="n">
         <v>12</v>
@@ -7233,21 +8189,28 @@
       <c r="P51" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" s="13"/>
-      <c r="R51" s="13"/>
+      <c r="Q51" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="R51" s="13" t="s">
+        <v>362</v>
+      </c>
       <c r="S51" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T51" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="U51" s="14"/>
-      <c r="V51" s="14"/>
-      <c r="W51" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U51" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="V51" s="13"/>
+      <c r="W51" s="13"/>
+      <c r="X51" s="13"/>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>231</v>
+        <v>364</v>
       </c>
       <c r="B52" s="10" t="n">
         <v>0</v>
@@ -7295,21 +8258,26 @@
       <c r="P52" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" s="13"/>
+      <c r="Q52" s="13" t="s">
+        <v>365</v>
+      </c>
       <c r="R52" s="13"/>
       <c r="S52" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T52" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="U52" s="14"/>
-      <c r="V52" s="14"/>
-      <c r="W52" s="14"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>87</v>
+      </c>
+      <c r="T52" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="U52" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="V52" s="15"/>
+      <c r="W52" s="15"/>
+      <c r="X52" s="15"/>
+    </row>
+    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>233</v>
+        <v>367</v>
       </c>
       <c r="B53" s="10" t="n">
         <v>0</v>
@@ -7357,21 +8325,28 @@
       <c r="P53" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" s="13"/>
-      <c r="R53" s="13"/>
+      <c r="Q53" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="R53" s="13" t="s">
+        <v>369</v>
+      </c>
       <c r="S53" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T53" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="U53" s="14"/>
-      <c r="V53" s="14"/>
-      <c r="W53" s="14"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U53" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="V53" s="13"/>
+      <c r="W53" s="13"/>
+      <c r="X53" s="13"/>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>235</v>
+        <v>371</v>
       </c>
       <c r="B54" s="10" t="n">
         <v>21</v>
@@ -7419,21 +8394,28 @@
       <c r="P54" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" s="13"/>
-      <c r="R54" s="13"/>
+      <c r="Q54" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="R54" s="13" t="s">
+        <v>342</v>
+      </c>
       <c r="S54" s="13" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
       <c r="T54" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="U54" s="14"/>
-      <c r="V54" s="14"/>
-      <c r="W54" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U54" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="V54" s="13"/>
+      <c r="W54" s="13"/>
+      <c r="X54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>237</v>
+        <v>374</v>
       </c>
       <c r="B55" s="10" t="n">
         <v>11</v>
@@ -7481,21 +8463,28 @@
       <c r="P55" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" s="13"/>
-      <c r="R55" s="13"/>
+      <c r="Q55" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="R55" s="13" t="s">
+        <v>376</v>
+      </c>
       <c r="S55" s="13" t="s">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="T55" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="U55" s="14"/>
-      <c r="V55" s="14"/>
-      <c r="W55" s="14"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U55" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="V55" s="13"/>
+      <c r="W55" s="13"/>
+      <c r="X55" s="13"/>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
-        <v>239</v>
+        <v>378</v>
       </c>
       <c r="B56" s="10" t="n">
         <v>20</v>
@@ -7543,21 +8532,26 @@
       <c r="P56" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" s="13"/>
+      <c r="Q56" s="13" t="s">
+        <v>379</v>
+      </c>
       <c r="R56" s="13"/>
       <c r="S56" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T56" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="U56" s="14"/>
-      <c r="V56" s="14"/>
-      <c r="W56" s="14"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U56" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="V56" s="13"/>
+      <c r="W56" s="13"/>
+      <c r="X56" s="13"/>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>241</v>
+        <v>381</v>
       </c>
       <c r="B57" s="10" t="n">
         <v>15</v>
@@ -7605,21 +8599,28 @@
       <c r="P57" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" s="13"/>
-      <c r="R57" s="13"/>
+      <c r="Q57" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="R57" s="13" t="s">
+        <v>342</v>
+      </c>
       <c r="S57" s="13" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
       <c r="T57" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="U57" s="14"/>
-      <c r="V57" s="14"/>
-      <c r="W57" s="14"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U57" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="V57" s="13"/>
+      <c r="W57" s="13"/>
+      <c r="X57" s="13"/>
+    </row>
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9" t="s">
-        <v>243</v>
+        <v>384</v>
       </c>
       <c r="B58" s="10" t="n">
         <v>11</v>
@@ -7667,21 +8668,28 @@
       <c r="P58" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" s="13"/>
-      <c r="R58" s="13"/>
+      <c r="Q58" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="R58" s="13" t="s">
+        <v>342</v>
+      </c>
       <c r="S58" s="13" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
       <c r="T58" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="U58" s="14"/>
-      <c r="V58" s="14"/>
-      <c r="W58" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U58" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="V58" s="13"/>
+      <c r="W58" s="13"/>
+      <c r="X58" s="13"/>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="s">
-        <v>245</v>
+        <v>387</v>
       </c>
       <c r="B59" s="10" t="n">
         <v>2</v>
@@ -7729,21 +8737,26 @@
       <c r="P59" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" s="13"/>
+      <c r="Q59" s="13" t="s">
+        <v>388</v>
+      </c>
       <c r="R59" s="13"/>
       <c r="S59" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T59" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="U59" s="14"/>
-      <c r="V59" s="14"/>
-      <c r="W59" s="14"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U59" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="V59" s="13"/>
+      <c r="W59" s="13"/>
+      <c r="X59" s="13"/>
+    </row>
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="B60" s="10" t="n">
         <v>4</v>
@@ -7791,21 +8804,28 @@
       <c r="P60" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" s="13"/>
-      <c r="R60" s="13"/>
+      <c r="Q60" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="R60" s="13" t="s">
+        <v>391</v>
+      </c>
       <c r="S60" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T60" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="U60" s="14"/>
-      <c r="V60" s="14"/>
-      <c r="W60" s="14"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U60" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="V60" s="13"/>
+      <c r="W60" s="13"/>
+      <c r="X60" s="13"/>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="9" t="s">
-        <v>248</v>
+        <v>393</v>
       </c>
       <c r="B61" s="10" t="n">
         <v>0</v>
@@ -7853,21 +8873,28 @@
       <c r="P61" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" s="13"/>
-      <c r="R61" s="13"/>
+      <c r="Q61" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="R61" s="13" t="s">
+        <v>342</v>
+      </c>
       <c r="S61" s="13" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
       <c r="T61" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="U61" s="14"/>
-      <c r="V61" s="14"/>
-      <c r="W61" s="14"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U61" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="V61" s="13"/>
+      <c r="W61" s="13"/>
+      <c r="X61" s="13"/>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="s">
-        <v>250</v>
+        <v>396</v>
       </c>
       <c r="B62" s="10" t="n">
         <v>0</v>
@@ -7915,21 +8942,28 @@
       <c r="P62" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" s="13"/>
-      <c r="R62" s="13"/>
+      <c r="Q62" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="R62" s="13" t="s">
+        <v>342</v>
+      </c>
       <c r="S62" s="13" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
       <c r="T62" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="U62" s="14"/>
-      <c r="V62" s="14"/>
-      <c r="W62" s="14"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U62" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="V62" s="13"/>
+      <c r="W62" s="13"/>
+      <c r="X62" s="13"/>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
-        <v>251</v>
+        <v>398</v>
       </c>
       <c r="B63" s="10" t="n">
         <v>1</v>
@@ -7977,21 +9011,28 @@
       <c r="P63" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" s="13"/>
-      <c r="R63" s="13"/>
+      <c r="Q63" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="R63" s="13" t="s">
+        <v>347</v>
+      </c>
       <c r="S63" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T63" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="U63" s="14"/>
-      <c r="V63" s="14"/>
-      <c r="W63" s="14"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U63" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="V63" s="13"/>
+      <c r="W63" s="13"/>
+      <c r="X63" s="13"/>
+    </row>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
-        <v>253</v>
+        <v>401</v>
       </c>
       <c r="B64" s="10" t="n">
         <v>1</v>
@@ -8039,21 +9080,28 @@
       <c r="P64" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" s="13"/>
-      <c r="R64" s="13"/>
+      <c r="Q64" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="R64" s="13" t="s">
+        <v>402</v>
+      </c>
       <c r="S64" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T64" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="U64" s="14"/>
-      <c r="V64" s="14"/>
-      <c r="W64" s="14"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U64" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="V64" s="13"/>
+      <c r="W64" s="13"/>
+      <c r="X64" s="13"/>
+    </row>
+    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="s">
-        <v>255</v>
+        <v>404</v>
       </c>
       <c r="B65" s="10" t="n">
         <v>1</v>
@@ -8101,21 +9149,26 @@
       <c r="P65" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" s="13"/>
+      <c r="Q65" s="13" t="s">
+        <v>405</v>
+      </c>
       <c r="R65" s="13"/>
       <c r="S65" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T65" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="U65" s="14"/>
-      <c r="V65" s="14"/>
-      <c r="W65" s="14"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U65" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="V65" s="13"/>
+      <c r="W65" s="13"/>
+      <c r="X65" s="13"/>
+    </row>
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
-        <v>257</v>
+        <v>407</v>
       </c>
       <c r="B66" s="10" t="n">
         <v>1</v>
@@ -8163,21 +9216,28 @@
       <c r="P66" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" s="13"/>
-      <c r="R66" s="13"/>
+      <c r="Q66" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="R66" s="13" t="s">
+        <v>409</v>
+      </c>
       <c r="S66" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T66" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="U66" s="14"/>
-      <c r="V66" s="14"/>
-      <c r="W66" s="14"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U66" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="V66" s="13"/>
+      <c r="W66" s="13"/>
+      <c r="X66" s="13"/>
+    </row>
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>259</v>
+        <v>411</v>
       </c>
       <c r="B67" s="10" t="n">
         <v>1</v>
@@ -8225,21 +9285,26 @@
       <c r="P67" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" s="13"/>
+      <c r="Q67" s="13" t="s">
+        <v>412</v>
+      </c>
       <c r="R67" s="13"/>
       <c r="S67" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T67" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="U67" s="14"/>
-      <c r="V67" s="14"/>
-      <c r="W67" s="14"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="U67" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="V67" s="13"/>
+      <c r="W67" s="13"/>
+      <c r="X67" s="13"/>
+    </row>
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
-        <v>261</v>
+        <v>414</v>
       </c>
       <c r="B68" s="10" t="n">
         <v>0</v>
@@ -8287,20 +9352,27 @@
       <c r="P68" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" s="13"/>
-      <c r="R68" s="13"/>
+      <c r="Q68" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="R68" s="13" t="s">
+        <v>416</v>
+      </c>
       <c r="S68" s="13" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="T68" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="U68" s="14"/>
-      <c r="V68" s="14"/>
-      <c r="W68" s="14"/>
+        <v>54</v>
+      </c>
+      <c r="U68" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="V68" s="13"/>
+      <c r="W68" s="13"/>
+      <c r="X68" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W68"/>
+  <autoFilter ref="A1:X68"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8325,205 +9397,205 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>263</v>
+      <c r="A1" s="16" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
-        <v>264</v>
+      <c r="A2" s="17" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>265</v>
+        <v>420</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>266</v>
+        <v>421</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>267</v>
+        <v>422</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>268</v>
+        <v>423</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>269</v>
+        <v>424</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>270</v>
+        <v>425</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>271</v>
+        <v>426</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>272</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="18" t="n">
+      <c r="A5" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="19" t="n">
         <v>27</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="19" t="n">
         <v>41</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>22911</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="19" t="n">
         <v>34925</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="19" t="n">
         <f aca="false">SUM(B5:G5)</f>
         <v>57957</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" s="18" t="n">
+      <c r="A6" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="19" t="n">
         <v>475</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="19" t="n">
         <v>117</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="19" t="n">
         <v>117</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <v>140</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>7168</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="19" t="n">
         <v>153</v>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="19" t="n">
         <f aca="false">SUM(B6:G6)</f>
         <v>8170</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="18" t="n">
+      <c r="A7" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="19" t="n">
         <v>307</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>56</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <v>9749</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>23590</v>
       </c>
-      <c r="G7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="18" t="n">
+      <c r="G7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="19" t="n">
         <f aca="false">SUM(B7:G7)</f>
         <v>33720</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="18" t="n">
+      <c r="A8" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="19" t="n">
         <v>58470</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>63503</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="19" t="n">
         <v>51231</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <v>83070</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>40392</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H8" s="19" t="n">
         <f aca="false">SUM(B8:G8)</f>
         <v>296672</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="B9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="18" t="n">
+      <c r="A9" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="19" t="n">
         <v>26255</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="19" t="n">
         <f aca="false">SUM(B9:G9)</f>
         <v>26255</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="B10" s="19" t="n">
+      <c r="A10" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="B10" s="20" t="n">
         <f aca="false">SUM(B5:B9)</f>
         <v>59275</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="20" t="n">
         <f aca="false">SUM(C5:C9)</f>
         <v>63703</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="20" t="n">
         <f aca="false">SUM(D5:D9)</f>
         <v>61127</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">SUM(E5:E9)</f>
         <v>83269</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="20" t="n">
         <f aca="false">SUM(F5:F9)</f>
         <v>94061</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">SUM(G5:G9)</f>
         <v>61339</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="20" t="n">
         <f aca="false">SUM(H5:H9)</f>
         <v>422774</v>
       </c>

--- a/exports/pm06_status_codes.xlsx
+++ b/exports/pm06_status_codes.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="428">
   <si>
     <t xml:space="preserve">Коды статусов заказов ТОРО в выгрузке PM-06</t>
   </si>
@@ -218,13 +218,10 @@
     <t xml:space="preserve">Задача завершена</t>
   </si>
   <si>
-    <t xml:space="preserve">Текст из SAP. Стоит на 99 % технически и коммерчески закрытых заказов.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">скриншот окна статусов SAP (Статусы.docx); вывод по данным PM-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">текст подтверждён</t>
+    <t xml:space="preserve">Текст из SAP. Стоит на 99 % технически и коммерчески закрытых заказов. Заказ не закрывает.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">скриншот окна статусов SAP (Статусы.docx); вывод по данным PM-06; заполнено пользователем (Order_status_codes.xlsx)</t>
   </si>
   <si>
     <t xml:space="preserve">ЗАКР</t>
@@ -242,862 +239,865 @@
     <t xml:space="preserve">ДВМА</t>
   </si>
   <si>
-    <t xml:space="preserve">Вероятно «Движение материала проведено» (GMPS): у 99–100 % таких заказов есть факт.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стандартная расшифровка SAP; вывод по данным PM-06</t>
+    <t xml:space="preserve">Движение материала произошло</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вероятно «Движение материала проведено» (GMPS): у 99–100 % таких заказов есть факт. Заказ не закрывает.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">заполнено пользователем (Order_status_codes.xlsx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПДТВ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подтверждено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Введены подтверждения по всем операциям; только при ДЕБЛ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1100884694; 2024 1100 1101259617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РБЗК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Работа закрыта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Текст из SAP. Появляется с 2024 года вместе с АНРЕ и АРВО на закрываемых заказах.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024 1100 1101813707; 2025 1100 1101878222; 2026 1100 1200365166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АНРЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анализ результатов проведен</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Текст из SAP. С 2024 года, всегда вместе с АРВО. Заказ не закрывает.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">скриншот окна статусов SAP (Статусы.docx); заполнено пользователем (Order_status_codes.xlsx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024 1100 1101813707; 2025 1100 1101878222; 2026 1100 1102226644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АРВО</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С 2024 года, всегда вместе с АНРЕ и РБЗК. Расшифровки в документации нет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПЕЧТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Напечатано</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказ распечатан; только при ДЕБЛ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100759462; 2023 1100 1100877483; 2024 1100 1101392569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KKMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Без компонентов материала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически, если в заказе нет материалов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100771390; 2023 1100 1100910354; 2024 1100 1200252523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОТКР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Открыто</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставится автоматически при создании заказа. Заказ ещё не деблокирован.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1800010075; 2023 1100 1101471084; 2024 1100 1101879322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЧПЕЧ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Частично напечатано</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Напечатана часть документов заказа. Заказ не закрывает.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100386576; 2023 1100 1101045267; 2024 1100 1100884889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЧПДТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Частично подтверждено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подтверждена часть операций; только при ДЕБЛ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100317458; 2023 1100 1100877483; 2024 1100 1100884889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СРНА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сроки не актуальны</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Даты заказа не пересчитаны (NTUP).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">скриншот окна статусов SAP (Статусы.docx); стандартная расшифровка SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100386045; 2023 1100 1101340657; 2024 1100 1101392569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТЗКР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Технически закрыто</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Техническое закрытие: работы выполнены, факт проведён. Ставит планировщик ТОиР; только при ДЕБЛ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19; ТОиР-84; памятка ТОиР-77 «Ключевые отличия SAP ТОРО в АО Развитие»; спецификация отчёта, лист «Алгоритмы выборки»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1200090088; 2023 1100 1003960; 2024 1100 1101926982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">нет статуса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Позиция графика ППР без заказа SAP. Не заказ и не входит в план: в план и потребность не включать.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">подтверждено пользователем; КД ERP.13.9.2.52 табл. 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027 1100 110000033568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ошибка при определении затрат</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказ не закрывает.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100317017; 2023 1100 1200159659; 2024 1100 1900003788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ДЕБЛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Деблокировано</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказ передан в работу: разрешены печать и фактические проводки.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 4000018911; 2023 1100 4000036509; 2024 1100 4000040107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Завершение подтверждено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1100 1101948705; 2026 1100 1102683820; 2025 1200 1101767962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Данные на мобильном устройстве</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98 % на заказах ЕТО (AETG): вероятно, передача на мобильное устройство. Заказ не закрывает.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1100 1600682946; 2026 1100 1600871206; 2022 1200 1100356263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НКС</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Есть незавершённое капитальное строительство</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КООП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Контировка операции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НОСР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Только сетевые графики P310. Расшифровки в документации нет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 4000009964; 2023 1300 4000030482; 2022 1400 4000018391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ДВЖМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Движение материала в СетГрЗаказов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100439271; 2023 1100 1100883152; 2024 1100 1100884889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПОСТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поставлено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вероятно «Поставлено» (DLV); только на заказах вспомогательного производства ZP01. Заказ не закрывает.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1001765; 2023 1100 1003960; 2024 1100 1004640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РОСГ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Только заказы вспомогательного производства ZP01. Расшифровки в документации нет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НРАК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОБВП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЧДЕБ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Частично деблокировано</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В выгрузке встречается только на сетевых графиках P310/P030. Заказ не закрывает.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 4000009964; 2025 1100 4000053526; 2026 1100 4000065249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ДЕБО</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Деблокирование отклонено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027 1100 1500038731; 2026 1400 1102333756; 2027 1400 1500030652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МАПД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Материал подтвержден</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверка доступности запущена, все материалы подтверждены.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1002218; 2023 1100 1004152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЗАОЦ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Затраты оценены</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1200100075; 2026 1100 910100045331; 2023 1300 910100027096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЗТНА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Затраты не актуальны</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 4000015921; 2024 1100 4000041533; 2022 1400 4000018125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НПДМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доступность мощностей не проверена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 2000021301; 2023 1400 2000045981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НМАТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нет материала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 заказа 2022 года; стандартный системный статус NMAT. В актуальной схеме «Нет материалов» — пользовательский статус. Заказ не закрывает.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1002186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СГГС</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согл Гл спец ТОиР БЕ ГОК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Порядковый №4: согласовано главным специалистом ТОиР.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МТРЦ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МТР оценены</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически: цены всех МТР утверждены.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19 (табл. 18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ГОД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказ включен в годовой план</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставит планировщик ТОиР после включения в годовой план.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1100884694; 2024 1100 1100884889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРНТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Работы приняты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Инженер ТОиР принял работы; условие ТЗКР для заказов с УСО.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19 (табл. 18); ТОиР-77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100480386; 2023 1100 1100821797; 2024 1100 1900003446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ГИП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согласован Главным инженером</t>
+  </si>
+  <si>
+    <t xml:space="preserve">После утверждения плана-графика главным инженером и согласования ПТО.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРСЗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Принято службой заказчика</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Приёмка работ АО «Развитие» службой заказчика БЕ; только после ТЗКР. Блокирует дальнейшие проводки.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">памятка ТОиР-77 «Ключевые отличия SAP ТОРО в АО Развитие»; ТОиР-84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ВСБЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказ выставлен в БЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически при регистрации выручки (ZMM_370); после него снять ПРСЗ нельзя.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">памятка ТОиР-77 «Ключевые отличия SAP ТОРО в АО Развитие»; скриншот окна статусов SAP (Статусы.docx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СРОЧ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Срочная закупка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически: дата потребности раньше даты поставки МТР (с учётом остатков и LT).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19 (табл. 18); ТОиР-86, ТОиР-96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">УТВГ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утвержден в программе ремонтов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставит старший планировщик после утверждения годового плана-графика.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100316544; 2023 1100 1100884694; 2024 1100 1100884889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МЕС</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказ включен в месячный план</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставит планировщик.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1100884048; 2024 1100 1100884889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">УТВМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утв в месячном плане-графике</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставит старший планировщик.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">УТВН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утв в недельном плане-графике</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НЕД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказ включен в недельный план</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1100910354; 2024 1100 1101259617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПЗТГ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согласован ПЗТГ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согласован прогноз завершения текущего года; ставится автоматически при отправке в ПТО.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19; КД ERP.13.9.2.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПТОГ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согл ПТО в год плане-графике</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Без него нельзя поставить ГИП.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023 1100 1100877483; 2024 1100 1100884889; 2025 1100 1101878222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПТОМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согл ПТО в мес плане-графике</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Месячное оперативное планирование.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100319664; 2023 1100 1100877483; 2024 1100 1100884889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТКБЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бюджет на год утвержден ТК БЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически из SAP MCB.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">УТВП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утв в программе и бюджете</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически после утверждения программы и бюджета (из SAP MCB).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СГЛБ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согл спец по бюджетированию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согласовано специалистом по бюджетированию.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">скриншот окна статусов SAP (Статусы.docx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1100 1102140603; 2026 1100 1102226644; 2027 1100 1500033040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ССПЛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согл Ст Пл ТОиР БЕ ГОК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Порядковый №3: согласовано старшим планировщиком; дальше заказ блокируется для изменений.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1500007834; 2023 1100 1500020529; 2024 1100 1500025393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФХСМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Факт ХС, РП, МТР полн.проведен</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Техник подтверждает, что затрат больше не будет; заказ готов к ТЗКР.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">памятка ТОиР-84; скриншот окна статусов SAP (Статусы.docx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1100 1200345311; 2024 1300 1101673514; 2025 1300 1101674364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РИПР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Работы исполнены подрядчиком</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1200 2000038452; 2023 1200 2000046506; 2022 1400 1100592636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1100 2100051692; 2027 1100 110000033568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РЗПР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Работы запланир. подрядчиком</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1200109732; 2023 1100 1200152116; 2024 1100 1200260702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПЛАН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Планируется</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Порядковый №1: начальный статус, ставится автоматически.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100374749; 2023 1100 1101471084; 2024 1100 1101963158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПЛЗК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Плановый заказ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100770856; 2023 1100 1100768199; 2024 1100 1101813707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КОРБ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бюджет выделен и скорректир-н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически по отдельному запросу.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100770915; 2023 1100 1100804673; 2024 1100 1101447598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КРМТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Капитализируемый ремонт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подпадает под критерии капитализации (CAPEX).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПЗТМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прогноз завершения месяца</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Воздействие согласовано в прогнозе завершения текущего месяца (срез КТГ).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">памятка ТОиР-66; скриншот окна статусов SAP (Статусы.docx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1101012151; 2024 1100 1101259207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МТРН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Материалы не оценены</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически: есть МТР без плановой цены.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100384609; 2023 1100 1101013018; 2024 1100 1101813707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НВСО</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Невостребованные остатки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Некорректируемый: ставится, когда удаляют законтрактованную потребность или закрывают заказ через ТЗКР, а материал уже закуплен.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">памятки ТОиР-75, ТОиР-96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100375001; 2023 1100 1900003604; 2024 1100 1100884889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СГПЛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отпр на согл Пл ТОиР БЕ ГОК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Порядковый №2: планировщик отправил заказ на согласование старшему планировщику.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1200128633; 2023 1100 1900003582; 2024 1100 1101267001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЗАПЛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запланирован</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Начальный статус схемы PM_ETO (ежесменное ТО).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19 табл. 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1600127329; 2025 1100 1600682946; 2026 1100 1600871206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТОПЗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Требуется опереж. закуп</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нужна опережающая закупка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1100 1101805027; 2027 1100 1102039908; 2026 1300 1102373845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРЭК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Принято эксплуатацией</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Приёмка подразделением эксплуатации.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1200085136; 2023 1100 1100798987; 2024 1100 1101195035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НДСГ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наряд-допуск согласован</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100386576; 2023 1100 1200144892; 2024 1100 1101259258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СОПЗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согласован опереж. закуп</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Опережающая закупка согласована.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027 1100 1102536315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПОЛН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказ наполнен вручную</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОЦЕН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Только сетевые графики P030. Расшифровки нет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТРКБ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Требуется коррект-ка бюджета</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Не хватает бюджета.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024 1100 1101350102; 2026 1100 1200469833; 2027 1400 1800018121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КОРР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Требует корректировки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">По листу замечаний; снимается после исправления.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100374749; 2023 1100 1100813704; 2024 1100 1500021284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МПРО</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Планир-е ОстРемонта выполнено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1100 1101831744; 2026 1100 1102077093; 2022 1200 1100362415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОСТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утвержден в графике ОстРемонта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100455986; 2023 1100 1100820844; 2024 1100 1101371043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МПРП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Планир-е ОстРемонт согласовано</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1100 1101831744; 2026 1100 1102077093; 2023 1300 1200166682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">УТВР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утверждено (на ИК УК)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Статус заявки на замену оборудования (ОВП, вид P310), а не заказа ТОРО.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КД ERP.13.9.2.73 «Планирование и согласование ОВП»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023 1300 4000033438; 2022 1400 4000018641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОТКБ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коррект-ка бюджета отклонена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматически.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 1100 1100420579; 2023 1100 1100824912; 2024 1100 1101967998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СИНХ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказы синхронизированы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Со смежными службами.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023 1400 1101038173; 2024 1400 1100825565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МТПЛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Материалы запланированы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Старая схема статусов (встречается только в 2022 году).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">документация (2 упоминания)</t>
   </si>
   <si>
     <t xml:space="preserve">вероятно</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПДТВ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подтверждено</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Введены подтверждения по всем операциям; только при ДЕБЛ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1100884694; 2024 1100 1101259617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РБЗК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Работа закрыта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Текст из SAP. Появляется с 2024 года вместе с АНРЕ и АРВО на закрываемых заказах.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">текст подтверждён, назначение — вывод по данным</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024 1100 1101813707; 2025 1100 1101878222; 2026 1100 1200365166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АНРЕ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Анализ результатов проведен</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Текст из SAP. С 2024 года, всегда вместе с АРВО.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">скриншот окна статусов SAP (Статусы.docx)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024 1100 1101813707; 2025 1100 1101878222; 2026 1100 1102226644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АРВО</t>
-  </si>
-  <si>
-    <t xml:space="preserve">С 2024 года, всегда вместе с АНРЕ и РБЗК. Расшифровки в документации нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПЕЧТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Напечатано</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказ распечатан; только при ДЕБЛ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100759462; 2023 1100 1100877483; 2024 1100 1101392569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KKMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Без компонентов материала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Автоматически, если в заказе нет материалов.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100771390; 2023 1100 1100910354; 2024 1100 1200252523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОТКР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Открыто</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ставится автоматически при создании заказа. Заказ ещё не деблокирован.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1800010075; 2023 1100 1101471084; 2024 1100 1101879322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЧПЕЧ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Частично напечатано</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Напечатана часть документов заказа.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стандартная расшифровка SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100386576; 2023 1100 1101045267; 2024 1100 1100884889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЧПДТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Частично подтверждено</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подтверждена часть операций; только при ДЕБЛ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100317458; 2023 1100 1100877483; 2024 1100 1100884889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СРНА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сроки не актуальны</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Даты заказа не пересчитаны (NTUP).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">скриншот окна статусов SAP (Статусы.docx); стандартная расшифровка SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100386045; 2023 1100 1101340657; 2024 1100 1101392569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТЗКР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Технически закрыто</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Техническое закрытие: работы выполнены, факт проведён. Ставит планировщик ТОиР; только при ДЕБЛ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19; ТОиР-84; памятка ТОиР-77 «Ключевые отличия SAP ТОРО в АО Развитие»; спецификация отчёта, лист «Алгоритмы выборки»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1200090088; 2023 1100 1003960; 2024 1100 1101926982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нет статуса</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Позиция графика ППР, по которой заказ SAP ещё не создан. Только 2027 год, номера из диапазона планов ТОРО 100000000000–199999999999.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">вывод по данным PM-06; КД ERP.13.9.2.52 табл. 25 (диапазон номеров планов ТОРО); ТОиР-82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">гипотеза, подкреплена документацией</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027 1100 110000033568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72 % на открытых заказах плана 2027 года. Расшифровки в документации нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100317017; 2023 1100 1200159659; 2024 1100 1900003788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ДЕБЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Деблокировано</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказ передан в работу: разрешены печать и фактические проводки.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 4000018911; 2023 1100 4000036509; 2024 1100 4000040107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95 % на технически закрытых заказах. Расшифровки в документации нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1100 1101948705; 2026 1100 1102683820; 2025 1200 1101767962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98 % на заказах ЕТО (AETG): вероятно, передача на мобильное устройство.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">гипотеза</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1100 1600682946; 2026 1100 1600871206; 2022 1200 1100356263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НКС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97 % на коммерчески закрытых заказах. Расшифровки в документации нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КООП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Только сетевые графики P030/P310. Расшифровки в документации нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НОСР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Только сетевые графики P310. Расшифровки в документации нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 4000009964; 2023 1300 4000030482; 2022 1400 4000018391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ДВЖМ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Рядом с ДВМА (движение материала). Расшифровки в документации нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100439271; 2023 1100 1100883152; 2024 1100 1100884889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПОСТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вероятно «Поставлено» (DLV); только на заказах вспомогательного производства ZP01.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1001765; 2023 1100 1003960; 2024 1100 1004640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РОСГ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Только заказы вспомогательного производства ZP01. Расшифровки в документации нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НРАК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОБВП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЧДЕБ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Частично деблокировано</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В выгрузке встречается только на сетевых графиках P310/P030.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 4000009964; 2025 1100 4000053526; 2026 1100 4000065249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ДЕБО</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48 открытых заказов. Расшифровки в документации нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027 1100 1500038731; 2026 1400 1102333756; 2027 1400 1500030652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МАПД</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Материал подтвержден</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Проверка доступности запущена, все материалы подтверждены.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1002218; 2023 1100 1004152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЗАОЦ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 заказов, в основном ASR1. Расшифровки в документации нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1200100075; 2026 1100 910100045331; 2023 1300 910100027096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЗТНА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Только сетевые графики P030. Расшифровки в документации нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 4000015921; 2024 1100 4000041533; 2022 1400 4000018125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НПДМ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 закрытых заказа. Расшифровки в документации нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 2000021301; 2023 1400 2000045981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НМАТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Нет материала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 заказа 2022 года; стандартный системный статус NMAT. В актуальной схеме «Нет материалов» — пользовательский статус.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1002186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СГГС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согл Гл спец ТОиР БЕ ГОК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Порядковый №4: согласовано главным специалистом ТОиР.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МТРЦ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МТР оценены</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Автоматически: цены всех МТР утверждены.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19 (табл. 18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ГОД</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказ включен в годовой план</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ставит планировщик ТОиР после включения в годовой план.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1100884694; 2024 1100 1100884889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПРНТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Работы приняты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Инженер ТОиР принял работы; условие ТЗКР для заказов с УСО.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19 (табл. 18); ТОиР-77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100480386; 2023 1100 1100821797; 2024 1100 1900003446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ГИП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согласован Главным инженером</t>
-  </si>
-  <si>
-    <t xml:space="preserve">После утверждения плана-графика главным инженером и согласования ПТО.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПРСЗ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Принято службой заказчика</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Приёмка работ АО «Развитие» службой заказчика БЕ; только после ТЗКР. Блокирует дальнейшие проводки.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">памятка ТОиР-77 «Ключевые отличия SAP ТОРО в АО Развитие»; ТОиР-84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ВСБЕ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказ выставлен в БЕ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Автоматически при регистрации выручки (ZMM_370); после него снять ПРСЗ нельзя.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">памятка ТОиР-77 «Ключевые отличия SAP ТОРО в АО Развитие»; скриншот окна статусов SAP (Статусы.docx)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СРОЧ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Срочная закупка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Автоматически: дата потребности раньше даты поставки МТР (с учётом остатков и LT).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19 (табл. 18); ТОиР-86, ТОиР-96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">УТВГ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Утвержден в программе ремонтов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ставит старший планировщик после утверждения годового плана-графика.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100316544; 2023 1100 1100884694; 2024 1100 1100884889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МЕС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказ включен в месячный план</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ставит планировщик.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1100884048; 2024 1100 1100884889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">УТВМ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Утв в месячном плане-графике</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ставит старший планировщик.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">УТВН</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Утв в недельном плане-графике</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НЕД</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказ включен в недельный план</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1100910354; 2024 1100 1101259617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПЗТГ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согласован ПЗТГ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согласован прогноз завершения текущего года; ставится автоматически при отправке в ПТО.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19; КД ERP.13.9.2.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПТОГ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согл ПТО в год плане-графике</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Без него нельзя поставить ГИП.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023 1100 1100877483; 2024 1100 1100884889; 2025 1100 1101878222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПТОМ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согл ПТО в мес плане-графике</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Месячное оперативное планирование.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100319664; 2023 1100 1100877483; 2024 1100 1100884889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТКБЕ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Бюджет на год утвержден ТК БЕ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Автоматически из SAP MCB.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">УТВП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Утв в программе и бюджете</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Автоматически после утверждения программы и бюджета (из SAP MCB).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СГЛБ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согл спец по бюджетированию</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согласовано специалистом по бюджетированию.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1100 1102140603; 2026 1100 1102226644; 2027 1100 1500033040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ССПЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согл Ст Пл ТОиР БЕ ГОК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Порядковый №3: согласовано старшим планировщиком; дальше заказ блокируется для изменений.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1500007834; 2023 1100 1500020529; 2024 1100 1500025393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ФХСМ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Факт ХС, РП, МТР полн.проведен</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Техник подтверждает, что затрат больше не будет; заказ готов к ТЗКР.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">памятка ТОиР-84; скриншот окна статусов SAP (Статусы.docx)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1100 1200345311; 2024 1300 1101673514; 2025 1300 1101674364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РИПР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Работы исполнены подрядчиком</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1200 2000038452; 2023 1200 2000046506; 2022 1400 1100592636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1100 2100051692; 2027 1100 110000033568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РЗПР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Работы запланир. подрядчиком</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1200109732; 2023 1100 1200152116; 2024 1100 1200260702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПЛАН</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Планируется</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Порядковый №1: начальный статус, ставится автоматически.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100374749; 2023 1100 1101471084; 2024 1100 1101963158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПЛЗК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Плановый заказ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100770856; 2023 1100 1100768199; 2024 1100 1101813707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КОРБ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Бюджет выделен и скорректир-н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Автоматически по отдельному запросу.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100770915; 2023 1100 1100804673; 2024 1100 1101447598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КРМТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Капитализируемый ремонт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подпадает под критерии капитализации (CAPEX).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПЗТМ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Прогноз завершения месяца</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Воздействие согласовано в прогнозе завершения текущего месяца (срез КТГ).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">памятка ТОиР-66; скриншот окна статусов SAP (Статусы.docx)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100386534; 2023 1100 1101012151; 2024 1100 1101259207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МТРН</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Материалы не оценены</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Автоматически: есть МТР без плановой цены.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100384609; 2023 1100 1101013018; 2024 1100 1101813707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НВСО</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Невостребованные остатки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Некорректируемый: ставится, когда удаляют законтрактованную потребность или закрывают заказ через ТЗКР, а материал уже закуплен.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">памятки ТОиР-75, ТОиР-96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100375001; 2023 1100 1900003604; 2024 1100 1100884889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СГПЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Отпр на согл Пл ТОиР БЕ ГОК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Порядковый №2: планировщик отправил заказ на согласование старшему планировщику.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1200128633; 2023 1100 1900003582; 2024 1100 1101267001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЗАПЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Запланирован</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Начальный статус схемы PM_ETO (ежесменное ТО).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КД ERP.13.9.2.52 «Годовое планирование», табл. 16–19 табл. 23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1600127329; 2025 1100 1600682946; 2026 1100 1600871206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТОПЗ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Требуется опереж. закуп</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Нужна опережающая закупка.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1100 1101805027; 2027 1100 1102039908; 2026 1300 1102373845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПРЭК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Принято эксплуатацией</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Приёмка подразделением эксплуатации.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1200085136; 2023 1100 1100798987; 2024 1100 1101195035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НДСГ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Наряд-допуск согласован</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100386576; 2023 1100 1200144892; 2024 1100 1101259258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СОПЗ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согласован опереж. закуп</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Опережающая закупка согласована.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027 1100 1102536315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПОЛН</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказ наполнен вручную</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОЦЕН</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Только сетевые графики P030. Расшифровки нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТРКБ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Требуется коррект-ка бюджета</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Не хватает бюджета.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024 1100 1101350102; 2026 1100 1200469833; 2027 1400 1800018121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КОРР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Требует корректировки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">По листу замечаний; снимается после исправления.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100374749; 2023 1100 1100813704; 2024 1100 1500021284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МПРО</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Планир-е ОстРемонта выполнено</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1100 1101831744; 2026 1100 1102077093; 2022 1200 1100362415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОСТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Утвержден в графике ОстРемонта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100455986; 2023 1100 1100820844; 2024 1100 1101371043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МПРП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Планир-е ОстРемонт согласовано</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1100 1101831744; 2026 1100 1102077093; 2023 1300 1200166682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">УТВР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Утверждено (на ИК УК)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Статус заявки на замену оборудования (ОВП, вид P310), а не заказа ТОРО.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КД ERP.13.9.2.73 «Планирование и согласование ОВП»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023 1300 4000033438; 2022 1400 4000018641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ОТКБ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Коррект-ка бюджета отклонена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Автоматически.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022 1100 1100420579; 2023 1100 1100824912; 2024 1100 1101967998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СИНХ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказы синхронизированы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Со смежными службами.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023 1400 1101038173; 2024 1400 1100825565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МТПЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Материалы запланированы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Старая схема статусов (встречается только в 2022 году).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">документация (2 упоминания)</t>
   </si>
   <si>
     <t xml:space="preserve">2022 1100 1001920</t>
@@ -2354,7 +2354,7 @@
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>61</v>
       </c>
@@ -2413,19 +2413,19 @@
       <c r="S6" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="T6" s="14" t="s">
-        <v>65</v>
+      <c r="T6" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U6" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="V6" s="15"/>
-      <c r="W6" s="15"/>
-      <c r="X6" s="15"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>58470</v>
@@ -2474,13 +2474,13 @@
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="R7" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="R7" s="13" t="s">
+      <c r="S7" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="S7" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="T7" s="13" t="s">
         <v>54</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>46266</v>
@@ -2542,26 +2542,28 @@
       <c r="P8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="13"/>
+      <c r="Q8" s="13" t="s">
+        <v>70</v>
+      </c>
       <c r="R8" s="13" t="s">
         <v>71</v>
       </c>
       <c r="S8" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="T8" s="14" t="s">
-        <v>73</v>
+      <c r="T8" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U8" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="15"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B9" s="10" t="n">
         <v>43887</v>
@@ -2610,19 +2612,19 @@
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="R9" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="R9" s="13" t="s">
+      <c r="S9" s="13" t="s">
         <v>76</v>
-      </c>
-      <c r="S9" s="13" t="s">
-        <v>77</v>
       </c>
       <c r="T9" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U9" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V9" s="13"/>
       <c r="W9" s="13"/>
@@ -2630,7 +2632,7 @@
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B10" s="10" t="n">
         <v>0</v>
@@ -2679,27 +2681,27 @@
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="R10" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="R10" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="S10" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="T10" s="14" t="s">
+      <c r="T10" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="U10" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="U10" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="V10" s="15"/>
-      <c r="W10" s="15"/>
-      <c r="X10" s="15"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>84</v>
       </c>
       <c r="B11" s="10" t="n">
         <v>0</v>
@@ -2748,27 +2750,27 @@
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="R11" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="S11" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="R11" s="13" t="s">
+      <c r="T11" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="U11" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="S11" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="T11" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="U11" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="V11" s="15"/>
-      <c r="W11" s="15"/>
-      <c r="X11" s="15"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B12" s="10" t="n">
         <v>0</v>
@@ -2818,7 +2820,7 @@
       </c>
       <c r="Q12" s="13"/>
       <c r="R12" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S12" s="13" t="s">
         <v>47</v>
@@ -2827,7 +2829,7 @@
         <v>48</v>
       </c>
       <c r="U12" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="V12" s="15"/>
       <c r="W12" s="15"/>
@@ -2835,7 +2837,7 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B13" s="10" t="n">
         <v>14724</v>
@@ -2884,19 +2886,19 @@
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="S13" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T13" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U13" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="V13" s="13"/>
       <c r="W13" s="13"/>
@@ -2904,7 +2906,7 @@
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>6213</v>
@@ -2953,10 +2955,10 @@
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S14" s="13" t="s">
         <v>53</v>
@@ -2965,7 +2967,7 @@
         <v>54</v>
       </c>
       <c r="U14" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="V14" s="13"/>
       <c r="W14" s="13"/>
@@ -2973,7 +2975,7 @@
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>23</v>
@@ -3022,19 +3024,19 @@
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R15" s="13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S15" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T15" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U15" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="V15" s="13"/>
       <c r="W15" s="13"/>
@@ -3042,7 +3044,7 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B16" s="10" t="n">
         <v>2897</v>
@@ -3091,27 +3093,27 @@
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="R16" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="S16" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="T16" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="U16" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="R16" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="S16" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="T16" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="U16" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
+      <c r="V16" s="13"/>
+      <c r="W16" s="13"/>
+      <c r="X16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B17" s="10" t="n">
         <v>2588</v>
@@ -3160,19 +3162,19 @@
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="S17" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T17" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U17" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="V17" s="13"/>
       <c r="W17" s="13"/>
@@ -3180,7 +3182,7 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B18" s="10" t="n">
         <v>6715</v>
@@ -3229,19 +3231,19 @@
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="R18" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="S18" s="13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="T18" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U18" s="13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="V18" s="13"/>
       <c r="W18" s="13"/>
@@ -3249,7 +3251,7 @@
     </row>
     <row r="19" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>307</v>
@@ -3298,27 +3300,27 @@
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="S19" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="T19" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U19" s="13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="V19" s="13"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
     </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B20" s="10" t="n">
         <v>0</v>
@@ -3367,23 +3369,23 @@
         <v>1</v>
       </c>
       <c r="Q20" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="R20" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="S20" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="T20" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="U20" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="R20" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="S20" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="T20" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="U20" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
@@ -3435,26 +3437,28 @@
       <c r="P21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="13"/>
+      <c r="Q21" s="13" t="s">
+        <v>124</v>
+      </c>
       <c r="R21" s="13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="S21" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T21" s="14" t="s">
-        <v>48</v>
+        <v>72</v>
+      </c>
+      <c r="T21" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U21" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="V21" s="15"/>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
+        <v>126</v>
+      </c>
+      <c r="V21" s="13"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>469</v>
@@ -3503,19 +3507,19 @@
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="R22" s="13" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T22" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U22" s="13" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="V22" s="13"/>
       <c r="W22" s="13"/>
@@ -3523,7 +3527,7 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>0</v>
@@ -3571,26 +3575,28 @@
       <c r="P23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="13"/>
+      <c r="Q23" s="13" t="s">
+        <v>132</v>
+      </c>
       <c r="R23" s="13" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T23" s="14" t="s">
-        <v>48</v>
+        <v>72</v>
+      </c>
+      <c r="T23" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U23" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
+        <v>133</v>
+      </c>
+      <c r="V23" s="13"/>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>556</v>
@@ -3638,26 +3644,28 @@
       <c r="P24" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" s="13"/>
+      <c r="Q24" s="13" t="s">
+        <v>135</v>
+      </c>
       <c r="R24" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S24" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T24" s="14" t="s">
-        <v>139</v>
+        <v>72</v>
+      </c>
+      <c r="T24" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U24" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="V24" s="15"/>
-      <c r="W24" s="15"/>
-      <c r="X24" s="15"/>
+        <v>137</v>
+      </c>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>875</v>
@@ -3705,26 +3713,28 @@
       <c r="P25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="13"/>
+      <c r="Q25" s="13" t="s">
+        <v>139</v>
+      </c>
       <c r="R25" s="13" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="S25" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T25" s="14" t="s">
-        <v>48</v>
+        <v>72</v>
+      </c>
+      <c r="T25" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U25" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>499</v>
@@ -3772,26 +3782,28 @@
       <c r="P26" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="13"/>
+      <c r="Q26" s="13" t="s">
+        <v>141</v>
+      </c>
       <c r="R26" s="13" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="S26" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T26" s="14" t="s">
-        <v>48</v>
+        <v>72</v>
+      </c>
+      <c r="T26" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U26" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="V26" s="15"/>
-      <c r="W26" s="15"/>
-      <c r="X26" s="15"/>
+        <v>130</v>
+      </c>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B27" s="10" t="n">
         <v>439</v>
@@ -3841,7 +3853,7 @@
       </c>
       <c r="Q27" s="13"/>
       <c r="R27" s="13" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="S27" s="13" t="s">
         <v>47</v>
@@ -3850,7 +3862,7 @@
         <v>48</v>
       </c>
       <c r="U27" s="13" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="V27" s="15"/>
       <c r="W27" s="15"/>
@@ -3858,7 +3870,7 @@
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B28" s="10" t="n">
         <v>48</v>
@@ -3906,26 +3918,28 @@
       <c r="P28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" s="13"/>
+      <c r="Q28" s="13" t="s">
+        <v>146</v>
+      </c>
       <c r="R28" s="13" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T28" s="14" t="s">
-        <v>48</v>
+        <v>72</v>
+      </c>
+      <c r="T28" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U28" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="V28" s="15"/>
-      <c r="W28" s="15"/>
-      <c r="X28" s="15"/>
+        <v>147</v>
+      </c>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B29" s="10" t="n">
         <v>298</v>
@@ -3973,26 +3987,28 @@
       <c r="P29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" s="13"/>
+      <c r="Q29" s="13" t="s">
+        <v>149</v>
+      </c>
       <c r="R29" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="S29" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="T29" s="14" t="s">
-        <v>73</v>
+      <c r="T29" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U29" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="V29" s="15"/>
-      <c r="W29" s="15"/>
-      <c r="X29" s="15"/>
+        <v>151</v>
+      </c>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B30" s="10" t="n">
         <v>292</v>
@@ -4042,7 +4058,7 @@
       </c>
       <c r="Q30" s="13"/>
       <c r="R30" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="S30" s="13" t="s">
         <v>47</v>
@@ -4051,7 +4067,7 @@
         <v>48</v>
       </c>
       <c r="U30" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V30" s="15"/>
       <c r="W30" s="15"/>
@@ -4059,7 +4075,7 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B31" s="10" t="n">
         <v>292</v>
@@ -4109,7 +4125,7 @@
       </c>
       <c r="Q31" s="13"/>
       <c r="R31" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="S31" s="13" t="s">
         <v>47</v>
@@ -4118,7 +4134,7 @@
         <v>48</v>
       </c>
       <c r="U31" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V31" s="15"/>
       <c r="W31" s="15"/>
@@ -4126,7 +4142,7 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B32" s="10" t="n">
         <v>292</v>
@@ -4176,7 +4192,7 @@
       </c>
       <c r="Q32" s="13"/>
       <c r="R32" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="S32" s="13" t="s">
         <v>47</v>
@@ -4185,7 +4201,7 @@
         <v>48</v>
       </c>
       <c r="U32" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V32" s="15"/>
       <c r="W32" s="15"/>
@@ -4193,7 +4209,7 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B33" s="10" t="n">
         <v>6</v>
@@ -4242,27 +4258,27 @@
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="R33" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="S33" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="T33" s="14" t="s">
-        <v>73</v>
+      <c r="T33" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U33" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="V33" s="15"/>
-      <c r="W33" s="15"/>
-      <c r="X33" s="15"/>
+        <v>159</v>
+      </c>
+      <c r="V33" s="13"/>
+      <c r="W33" s="13"/>
+      <c r="X33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B34" s="10" t="n">
         <v>0</v>
@@ -4310,26 +4326,28 @@
       <c r="P34" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" s="13"/>
+      <c r="Q34" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="R34" s="13" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="S34" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T34" s="14" t="s">
-        <v>48</v>
+        <v>72</v>
+      </c>
+      <c r="T34" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U34" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="V34" s="15"/>
-      <c r="W34" s="15"/>
-      <c r="X34" s="15"/>
+        <v>162</v>
+      </c>
+      <c r="V34" s="13"/>
+      <c r="W34" s="13"/>
+      <c r="X34" s="13"/>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B35" s="10" t="n">
         <v>20</v>
@@ -4378,19 +4396,19 @@
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="R35" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="S35" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T35" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U35" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V35" s="13"/>
       <c r="W35" s="13"/>
@@ -4398,7 +4416,7 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B36" s="10" t="n">
         <v>7</v>
@@ -4446,26 +4464,28 @@
       <c r="P36" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" s="13"/>
+      <c r="Q36" s="13" t="s">
+        <v>168</v>
+      </c>
       <c r="R36" s="13" t="s">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="S36" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T36" s="14" t="s">
-        <v>48</v>
+        <v>72</v>
+      </c>
+      <c r="T36" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U36" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
+        <v>169</v>
+      </c>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B37" s="10" t="n">
         <v>5</v>
@@ -4513,26 +4533,28 @@
       <c r="P37" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" s="13"/>
+      <c r="Q37" s="13" t="s">
+        <v>171</v>
+      </c>
       <c r="R37" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="S37" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="T37" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="U37" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="S37" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T37" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="U37" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
-      <c r="X37" s="15"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="B38" s="10" t="n">
         <v>2</v>
@@ -4580,26 +4602,28 @@
       <c r="P38" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" s="13"/>
+      <c r="Q38" s="13" t="s">
+        <v>174</v>
+      </c>
       <c r="R38" s="13" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="S38" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T38" s="14" t="s">
-        <v>48</v>
+        <v>72</v>
+      </c>
+      <c r="T38" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U38" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="V38" s="15"/>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
+        <v>175</v>
+      </c>
+      <c r="V38" s="13"/>
+      <c r="W38" s="13"/>
+      <c r="X38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B39" s="10" t="n">
         <v>2</v>
@@ -4648,23 +4672,23 @@
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="R39" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="S39" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="T39" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="U39" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="R39" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="S39" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="T39" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="U39" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="V39" s="15"/>
-      <c r="W39" s="15"/>
-      <c r="X39" s="15"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:X39"/>
@@ -4778,7 +4802,7 @@
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B2" s="10" t="n">
         <v>52170</v>
@@ -4827,10 +4851,10 @@
         <v>0</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="R2" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="S2" s="13" t="s">
         <v>53</v>
@@ -4847,7 +4871,7 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B3" s="10" t="n">
         <v>51506</v>
@@ -4896,13 +4920,13 @@
         <v>0</v>
       </c>
       <c r="Q3" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="S3" s="13" t="s">
         <v>186</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="S3" s="13" t="s">
-        <v>188</v>
       </c>
       <c r="T3" s="13" t="s">
         <v>54</v>
@@ -4916,7 +4940,7 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B4" s="10" t="n">
         <v>26998</v>
@@ -4965,19 +4989,19 @@
         <v>0</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="S4" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T4" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U4" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="V4" s="13"/>
       <c r="W4" s="13"/>
@@ -4985,7 +5009,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B5" s="10" t="n">
         <v>15159</v>
@@ -5034,19 +5058,19 @@
         <v>0</v>
       </c>
       <c r="Q5" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="S5" s="13" t="s">
         <v>194</v>
-      </c>
-      <c r="R5" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="S5" s="13" t="s">
-        <v>196</v>
       </c>
       <c r="T5" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U5" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
@@ -5054,7 +5078,7 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>25540</v>
@@ -5103,19 +5127,19 @@
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="R6" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S6" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T6" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U6" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="V6" s="13"/>
       <c r="W6" s="13"/>
@@ -5123,7 +5147,7 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>0</v>
@@ -5172,19 +5196,19 @@
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="S7" s="13" t="s">
         <v>202</v>
-      </c>
-      <c r="R7" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="S7" s="13" t="s">
-        <v>204</v>
       </c>
       <c r="T7" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U7" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V7" s="13"/>
       <c r="W7" s="13"/>
@@ -5192,7 +5216,7 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>0</v>
@@ -5241,19 +5265,19 @@
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="R8" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="S8" s="13" t="s">
         <v>206</v>
-      </c>
-      <c r="R8" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="S8" s="13" t="s">
-        <v>208</v>
       </c>
       <c r="T8" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U8" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V8" s="13"/>
       <c r="W8" s="13"/>
@@ -5261,7 +5285,7 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9" s="10" t="n">
         <v>18655</v>
@@ -5310,13 +5334,13 @@
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="S9" s="13" t="s">
         <v>210</v>
-      </c>
-      <c r="R9" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="S9" s="13" t="s">
-        <v>212</v>
       </c>
       <c r="T9" s="13" t="s">
         <v>54</v>
@@ -5330,7 +5354,7 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10" s="10" t="n">
         <v>15149</v>
@@ -5379,19 +5403,19 @@
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="R10" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="S10" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T10" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U10" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="V10" s="13"/>
       <c r="W10" s="13"/>
@@ -5399,7 +5423,7 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B11" s="10" t="n">
         <v>21688</v>
@@ -5448,19 +5472,19 @@
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="S11" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T11" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U11" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="V11" s="13"/>
       <c r="W11" s="13"/>
@@ -5468,7 +5492,7 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B12" s="10" t="n">
         <v>20618</v>
@@ -5517,19 +5541,19 @@
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="R12" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="S12" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T12" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U12" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="V12" s="13"/>
       <c r="W12" s="13"/>
@@ -5537,7 +5561,7 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B13" s="10" t="n">
         <v>23580</v>
@@ -5586,19 +5610,19 @@
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="S13" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T13" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U13" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="V13" s="13"/>
       <c r="W13" s="13"/>
@@ -5606,7 +5630,7 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>18365</v>
@@ -5655,19 +5679,19 @@
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="S14" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T14" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U14" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V14" s="13"/>
       <c r="W14" s="13"/>
@@ -5675,7 +5699,7 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>19235</v>
@@ -5724,19 +5748,19 @@
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="S15" s="13" t="s">
         <v>230</v>
-      </c>
-      <c r="R15" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="S15" s="13" t="s">
-        <v>232</v>
       </c>
       <c r="T15" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U15" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="V15" s="13"/>
       <c r="W15" s="13"/>
@@ -5744,7 +5768,7 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B16" s="10" t="n">
         <v>4387</v>
@@ -5793,19 +5817,19 @@
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="S16" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T16" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U16" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="V16" s="13"/>
       <c r="W16" s="13"/>
@@ -5813,7 +5837,7 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B17" s="10" t="n">
         <v>5847</v>
@@ -5862,19 +5886,19 @@
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="S17" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T17" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U17" s="13" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="V17" s="13"/>
       <c r="W17" s="13"/>
@@ -5882,7 +5906,7 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B18" s="10" t="n">
         <v>13027</v>
@@ -5931,19 +5955,19 @@
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="R18" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="S18" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T18" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U18" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="V18" s="13"/>
       <c r="W18" s="13"/>
@@ -5951,7 +5975,7 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>11151</v>
@@ -6000,19 +6024,19 @@
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="S19" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T19" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U19" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="V19" s="13"/>
       <c r="W19" s="13"/>
@@ -6020,7 +6044,7 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B20" s="10" t="n">
         <v>0</v>
@@ -6069,27 +6093,27 @@
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="R20" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="S20" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="R20" s="13" t="s">
+      <c r="T20" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="U20" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="S20" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="T20" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="U20" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B21" s="10" t="n">
         <v>4095</v>
@@ -6138,10 +6162,10 @@
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="R21" s="13" t="s">
         <v>252</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>253</v>
       </c>
       <c r="S21" s="13" t="s">
         <v>53</v>
@@ -6150,7 +6174,7 @@
         <v>54</v>
       </c>
       <c r="U21" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="V21" s="13"/>
       <c r="W21" s="13"/>
@@ -6158,7 +6182,7 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>0</v>
@@ -6207,19 +6231,19 @@
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="R22" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="R22" s="13" t="s">
+      <c r="S22" s="13" t="s">
         <v>257</v>
-      </c>
-      <c r="S22" s="13" t="s">
-        <v>258</v>
       </c>
       <c r="T22" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U22" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V22" s="13"/>
       <c r="W22" s="13"/>
@@ -6227,7 +6251,7 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>7194</v>
@@ -6276,25 +6300,25 @@
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="R23" s="13"/>
       <c r="S23" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="T23" s="14" t="s">
-        <v>65</v>
+        <v>248</v>
+      </c>
+      <c r="T23" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U23" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
-    </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>261</v>
+      </c>
+      <c r="V23" s="13"/>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>0</v>
@@ -6343,27 +6367,27 @@
         <v>1</v>
       </c>
       <c r="Q24" s="13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="R24" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="S24" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="T24" s="14" t="s">
-        <v>126</v>
+        <v>122</v>
+      </c>
+      <c r="T24" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U24" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="V24" s="15"/>
-      <c r="W24" s="15"/>
-      <c r="X24" s="15"/>
+        <v>262</v>
+      </c>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>6355</v>
@@ -6412,25 +6436,25 @@
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="R25" s="13"/>
       <c r="S25" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="T25" s="14" t="s">
-        <v>65</v>
+        <v>248</v>
+      </c>
+      <c r="T25" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U25" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
+        <v>265</v>
+      </c>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>24</v>
@@ -6479,10 +6503,10 @@
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="R26" s="13" t="s">
         <v>268</v>
-      </c>
-      <c r="R26" s="13" t="s">
-        <v>269</v>
       </c>
       <c r="S26" s="13" t="s">
         <v>53</v>
@@ -6491,7 +6515,7 @@
         <v>54</v>
       </c>
       <c r="U26" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="V26" s="13"/>
       <c r="W26" s="13"/>
@@ -6499,7 +6523,7 @@
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B27" s="10" t="n">
         <v>946</v>
@@ -6548,25 +6572,25 @@
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="R27" s="13"/>
       <c r="S27" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="T27" s="14" t="s">
-        <v>65</v>
+        <v>248</v>
+      </c>
+      <c r="T27" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U27" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="V27" s="15"/>
-      <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
+        <v>272</v>
+      </c>
+      <c r="V27" s="13"/>
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B28" s="10" t="n">
         <v>21</v>
@@ -6615,19 +6639,19 @@
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="R28" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="R28" s="13" t="s">
-        <v>276</v>
-      </c>
       <c r="S28" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T28" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U28" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="V28" s="13"/>
       <c r="W28" s="13"/>
@@ -6635,7 +6659,7 @@
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B29" s="10" t="n">
         <v>875</v>
@@ -6684,13 +6708,13 @@
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="R29" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="R29" s="13" t="s">
-        <v>280</v>
-      </c>
       <c r="S29" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T29" s="13" t="s">
         <v>54</v>
@@ -6704,7 +6728,7 @@
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B30" s="10" t="n">
         <v>1316</v>
@@ -6753,19 +6777,19 @@
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="R30" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="R30" s="13" t="s">
+      <c r="S30" s="13" t="s">
         <v>283</v>
-      </c>
-      <c r="S30" s="13" t="s">
-        <v>284</v>
       </c>
       <c r="T30" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U30" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="V30" s="13"/>
       <c r="W30" s="13"/>
@@ -6773,7 +6797,7 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B31" s="10" t="n">
         <v>306</v>
@@ -6822,19 +6846,19 @@
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="R31" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="R31" s="13" t="s">
-        <v>288</v>
-      </c>
       <c r="S31" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T31" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U31" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="V31" s="13"/>
       <c r="W31" s="13"/>
@@ -6842,7 +6866,7 @@
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B32" s="10" t="n">
         <v>2</v>
@@ -6891,19 +6915,19 @@
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="R32" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="R32" s="13" t="s">
+      <c r="S32" s="13" t="s">
         <v>292</v>
-      </c>
-      <c r="S32" s="13" t="s">
-        <v>293</v>
       </c>
       <c r="T32" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U32" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="V32" s="13"/>
       <c r="W32" s="13"/>
@@ -6911,7 +6935,7 @@
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B33" s="10" t="n">
         <v>636</v>
@@ -6960,10 +6984,10 @@
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="R33" s="13" t="s">
         <v>296</v>
-      </c>
-      <c r="R33" s="13" t="s">
-        <v>297</v>
       </c>
       <c r="S33" s="13" t="s">
         <v>53</v>
@@ -6972,7 +6996,7 @@
         <v>54</v>
       </c>
       <c r="U33" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="V33" s="13"/>
       <c r="W33" s="13"/>
@@ -6980,7 +7004,7 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B34" s="10" t="n">
         <v>1563</v>
@@ -7029,27 +7053,27 @@
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="R34" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="R34" s="13" t="s">
+      <c r="S34" s="13" t="s">
         <v>301</v>
-      </c>
-      <c r="S34" s="13" t="s">
-        <v>302</v>
       </c>
       <c r="T34" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U34" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="V34" s="13"/>
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
     </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B35" s="10" t="n">
         <v>0</v>
@@ -7098,27 +7122,27 @@
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="R35" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="R35" s="13" t="s">
+      <c r="S35" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="T35" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="U35" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="S35" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="T35" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="U35" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="V35" s="15"/>
-      <c r="W35" s="15"/>
-      <c r="X35" s="15"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B36" s="10" t="n">
         <v>346</v>
@@ -7167,19 +7191,19 @@
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="R36" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="R36" s="13" t="s">
-        <v>310</v>
-      </c>
       <c r="S36" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T36" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U36" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="V36" s="13"/>
       <c r="W36" s="13"/>
@@ -7187,7 +7211,7 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B37" s="10" t="n">
         <v>238</v>
@@ -7236,17 +7260,17 @@
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R37" s="13"/>
       <c r="S37" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T37" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U37" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="V37" s="13"/>
       <c r="W37" s="13"/>
@@ -7254,7 +7278,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B38" s="10" t="n">
         <v>0</v>
@@ -7303,27 +7327,27 @@
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="R38" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="R38" s="13" t="s">
+      <c r="S38" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="T38" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="U38" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="S38" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="T38" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="U38" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="V38" s="15"/>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
+      <c r="V38" s="13"/>
+      <c r="W38" s="13"/>
+      <c r="X38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B39" s="10" t="n">
         <v>205</v>
@@ -7372,17 +7396,17 @@
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="R39" s="13"/>
       <c r="S39" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T39" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U39" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="V39" s="13"/>
       <c r="W39" s="13"/>
@@ -7390,7 +7414,7 @@
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B40" s="10" t="n">
         <v>55</v>
@@ -7440,7 +7464,7 @@
       </c>
       <c r="Q40" s="13"/>
       <c r="R40" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="S40" s="13" t="s">
         <v>47</v>
@@ -7449,7 +7473,7 @@
         <v>48</v>
       </c>
       <c r="U40" s="13" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="V40" s="15"/>
       <c r="W40" s="15"/>
@@ -7457,7 +7481,7 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B41" s="10" t="n">
         <v>0</v>
@@ -7506,19 +7530,19 @@
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="R41" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="R41" s="13" t="s">
-        <v>325</v>
-      </c>
       <c r="S41" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T41" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U41" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="V41" s="13"/>
       <c r="W41" s="13"/>
@@ -7526,7 +7550,7 @@
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B42" s="10" t="n">
         <v>11</v>
@@ -7575,19 +7599,19 @@
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="R42" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="R42" s="13" t="s">
-        <v>329</v>
-      </c>
       <c r="S42" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T42" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U42" s="13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="V42" s="13"/>
       <c r="W42" s="13"/>
@@ -7595,7 +7619,7 @@
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B43" s="10" t="n">
         <v>260</v>
@@ -7644,17 +7668,17 @@
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="R43" s="13"/>
       <c r="S43" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T43" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U43" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="V43" s="13"/>
       <c r="W43" s="13"/>
@@ -7662,7 +7686,7 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B44" s="10" t="n">
         <v>178</v>
@@ -7711,17 +7735,17 @@
         <v>0</v>
       </c>
       <c r="Q44" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="R44" s="13"/>
       <c r="S44" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T44" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U44" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="V44" s="13"/>
       <c r="W44" s="13"/>
@@ -7729,7 +7753,7 @@
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B45" s="10" t="n">
         <v>257</v>
@@ -7778,17 +7802,17 @@
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="R45" s="13"/>
       <c r="S45" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T45" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U45" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="V45" s="13"/>
       <c r="W45" s="13"/>
@@ -7796,7 +7820,7 @@
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B46" s="10" t="n">
         <v>408</v>
@@ -7845,19 +7869,19 @@
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="R46" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="R46" s="13" t="s">
+      <c r="S46" s="13" t="s">
         <v>342</v>
-      </c>
-      <c r="S46" s="13" t="s">
-        <v>343</v>
       </c>
       <c r="T46" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U46" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="V46" s="13"/>
       <c r="W46" s="13"/>
@@ -7865,7 +7889,7 @@
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B47" s="10" t="n">
         <v>3</v>
@@ -7914,19 +7938,19 @@
         <v>0</v>
       </c>
       <c r="Q47" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="R47" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="R47" s="13" t="s">
-        <v>347</v>
-      </c>
       <c r="S47" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T47" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U47" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V47" s="13"/>
       <c r="W47" s="13"/>
@@ -7934,7 +7958,7 @@
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B48" s="10" t="n">
         <v>0</v>
@@ -7983,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="Q48" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="R48" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="R48" s="13" t="s">
-        <v>351</v>
-      </c>
       <c r="S48" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T48" s="13" t="s">
         <v>54</v>
       </c>
       <c r="U48" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="V48" s="13"/>
       <c r="W48" s="13"/>
@@ -8003,7 +8027,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B49" s="10" t="n">
         <v>47</v>
@@ -8052,16 +8076,16 @@
         <v>0</v>
       </c>
       <c r="Q49" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="R49" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="R49" s="13" t="s">
+      <c r="S49" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="S49" s="13" t="s">
+      <c r="T49" s="14" t="s">
         <v>356</v>
-      </c>
-      <c r="T49" s="14" t="s">
-        <v>73</v>
       </c>
       <c r="U49" s="13" t="s">
         <v>357</v>
@@ -8124,13 +8148,13 @@
         <v>359</v>
       </c>
       <c r="R50" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="S50" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="S50" s="13" t="s">
+      <c r="T50" s="14" t="s">
         <v>356</v>
-      </c>
-      <c r="T50" s="14" t="s">
-        <v>73</v>
       </c>
       <c r="U50" s="13" t="s">
         <v>357</v>
@@ -8196,7 +8220,7 @@
         <v>362</v>
       </c>
       <c r="S51" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T51" s="13" t="s">
         <v>54</v>
@@ -8263,17 +8287,17 @@
       </c>
       <c r="R52" s="13"/>
       <c r="S52" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="T52" s="14" t="s">
-        <v>65</v>
+        <v>248</v>
+      </c>
+      <c r="T52" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="U52" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="V52" s="15"/>
-      <c r="W52" s="15"/>
-      <c r="X52" s="15"/>
+      <c r="V52" s="13"/>
+      <c r="W52" s="13"/>
+      <c r="X52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
@@ -8332,7 +8356,7 @@
         <v>369</v>
       </c>
       <c r="S53" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T53" s="13" t="s">
         <v>54</v>
@@ -8398,10 +8422,10 @@
         <v>372</v>
       </c>
       <c r="R54" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="S54" s="13" t="s">
         <v>342</v>
-      </c>
-      <c r="S54" s="13" t="s">
-        <v>343</v>
       </c>
       <c r="T54" s="13" t="s">
         <v>54</v>
@@ -8470,7 +8494,7 @@
         <v>376</v>
       </c>
       <c r="S55" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="T55" s="13" t="s">
         <v>54</v>
@@ -8537,7 +8561,7 @@
       </c>
       <c r="R56" s="13"/>
       <c r="S56" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T56" s="13" t="s">
         <v>54</v>
@@ -8603,10 +8627,10 @@
         <v>382</v>
       </c>
       <c r="R57" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="S57" s="13" t="s">
         <v>342</v>
-      </c>
-      <c r="S57" s="13" t="s">
-        <v>343</v>
       </c>
       <c r="T57" s="13" t="s">
         <v>54</v>
@@ -8672,10 +8696,10 @@
         <v>385</v>
       </c>
       <c r="R58" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="S58" s="13" t="s">
         <v>342</v>
-      </c>
-      <c r="S58" s="13" t="s">
-        <v>343</v>
       </c>
       <c r="T58" s="13" t="s">
         <v>54</v>
@@ -8742,7 +8766,7 @@
       </c>
       <c r="R59" s="13"/>
       <c r="S59" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T59" s="13" t="s">
         <v>54</v>
@@ -8756,7 +8780,7 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B60" s="10" t="n">
         <v>4</v>
@@ -8811,7 +8835,7 @@
         <v>391</v>
       </c>
       <c r="S60" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T60" s="13" t="s">
         <v>54</v>
@@ -8877,10 +8901,10 @@
         <v>394</v>
       </c>
       <c r="R61" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="S61" s="13" t="s">
         <v>342</v>
-      </c>
-      <c r="S61" s="13" t="s">
-        <v>343</v>
       </c>
       <c r="T61" s="13" t="s">
         <v>54</v>
@@ -8946,10 +8970,10 @@
         <v>397</v>
       </c>
       <c r="R62" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="S62" s="13" t="s">
         <v>342</v>
-      </c>
-      <c r="S62" s="13" t="s">
-        <v>343</v>
       </c>
       <c r="T62" s="13" t="s">
         <v>54</v>
@@ -9015,10 +9039,10 @@
         <v>399</v>
       </c>
       <c r="R63" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="S63" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T63" s="13" t="s">
         <v>54</v>
@@ -9081,13 +9105,13 @@
         <v>0</v>
       </c>
       <c r="Q64" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="R64" s="13" t="s">
         <v>402</v>
       </c>
       <c r="S64" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T64" s="13" t="s">
         <v>54</v>
@@ -9154,7 +9178,7 @@
       </c>
       <c r="R65" s="13"/>
       <c r="S65" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T65" s="13" t="s">
         <v>54</v>
@@ -9223,7 +9247,7 @@
         <v>409</v>
       </c>
       <c r="S66" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T66" s="13" t="s">
         <v>54</v>
@@ -9290,7 +9314,7 @@
       </c>
       <c r="R67" s="13"/>
       <c r="S67" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T67" s="13" t="s">
         <v>54</v>
@@ -9359,7 +9383,7 @@
         <v>416</v>
       </c>
       <c r="S68" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T68" s="13" t="s">
         <v>54</v>
@@ -9434,7 +9458,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" s="19" t="n">
         <v>23</v>
@@ -9461,7 +9485,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B6" s="19" t="n">
         <v>475</v>
@@ -9488,7 +9512,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B7" s="19" t="n">
         <v>307</v>
@@ -9515,7 +9539,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B8" s="19" t="n">
         <v>58470</v>
@@ -9542,7 +9566,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B9" s="19" t="n">
         <v>0</v>
